--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0015.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0015.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Để lấy thêm điểm!</t>
+          <t>Để lấy điểm cộng!</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bạn nhìn theo hướng Grand Commander chỉ, giống như khi Joljodra chỉ về phía vị trí của Grand Commander.</t>
+          <t>Bạn nhìn theo hướng Đại Tư Lệnh chỉ, giống như khi Joljodra chỉ về phía vị trí của ông ta.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hãy nhìn các Knights of the Wild của chúng ta. Hãy đánh bại kẻ địch đang bao vây họ! Một khi họ hồi phục, họ sẽ cầm vũ khí chiến đấu bên cạnh bạn!</t>
+          <t>Hãy nhìn những Hiệp sĩ Hoang Dã của chúng ta. Hãy đánh bại kẻ thù đang bao vây họ! Một khi họ hồi phục, họ sẽ sát cánh cùng các ngươi!</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Các kỵ sĩ của ta hiểu rõ ý nghĩa của sự đoàn kết. Để thấy đồng đội được hỗ trợ kịp thời, những Kỵ Sĩ Common này sẽ Dodgem ngươi thẳng đến các Đại Kỵ Sĩ.</t>
+          <t>Các hiệp sĩ của ta hiểu rõ ý nghĩa của sự đoàn kết. Để thấy đồng đội được hỗ trợ kịp thời, những Hiệp Sĩ Thường này sẽ ném các ngươi thẳng đến Đại Hiệp Sĩ.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Nào, {PlayerName}, xin hãy… dẫn đầu cuộc tấn công!</t>
+          <t>Giờ thì, {PlayerName}, xin hãy... dẫn đầu cuộc tấn công!</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vì Astra, vì Caldheim, vì tất cả các Hiệp sĩ Hoang Dã!</t>
+          <t>Vì Astra, vì Caldheim, vì tất cả các Hiệp Sĩ Hoang Dã!</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tiến lên! Vào trận nào! Kỳ thi cuối sắp đến! Cố gắng kiếm thêm điểm thưởng đi!</t>
+          <t>Tiến lên! Chiến đấu nào! Kỳ thi cuối sắp đến! Cố gắng giành điểm cộng nhé!</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tiến lên! Vào trận nào! Vượt qua bài kiểm tra! Thưởng thêm điểm!!</t>
+          <t>Tiến lên! Chiến đấu nào! Vượt qua bài kiểm tra! Điểm cộng nào!!</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Không, tôi mong Đại Tư Lệnh hãy tự chăm sóc bản thân thật tốt. Nhưng xin hãy biết rằng tôi sẽ luôn là một hiệp sĩ của hội và sẽ đến trợ giúp bất cứ khi nào Ngài cần.</t>
+          <t>Không, ta mong ngài hãy bảo trọng, Đại Tư Lệnh. Nhưng hãy nhớ, ta sẽ luôn là một kỵ sĩ của hội, và sẽ đến trợ giúp ngài bất cứ khi nào cần.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Chúng tôi, những cỗ máy, không thể rơi lệ, nhưng tôi mong bạn biết rằng tôi vô cùng biết ơn.</t>
+          <t>Chúng tôi là máy móc, không thể rơi lệ... nhưng mong anh biết, lòng tôi tràn đầy biết ơn.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Tớ đồng ý!</t>
+          <t>Tôi đồng ý!</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>From now on, bạn có thể nhận "Khoản Thưởng Bổ Sung Từ Đại Tư Lệnh".</t>
+          <t>Từ giờ trở đi, ngươi có thể nhận được "Phụ Cấp Tổng Tư Lệnh Đặc Biệt".</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Tuy nhiên, sau việc này, tất cả lợi ích trước đây cậu nhận được sẽ biến mất. Nhưng đổi lại, cậu sẽ nhận được phần thưởng vô cùng hậu hĩnh.</t>
+          <t>Tuy nhiên, sau này, mọi lợi ích trước đây cậu có được sẽ dần tan biến. Nhưng đổi lại, cậu sẽ nhận được những phần thưởng vượt xa tưởng tượng.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Nhận Thưởng Tín Dụng Bổ Sung từ Grand Commander.</t>
+          <t>Nhận phần thưởng thêm của Đại Tư Lệnh</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dù chỉ còn lại thanh kiếm, ta vẫn sẽ vung lên và tiến về phía trước.</t>
+          <t>Dù chỉ còn lại thanh kiếm, ta vẫn sẽ tiến lên phía trước.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kiếm… kiếm nào cơ?</t>
+          <t>Kiếm… kiếm nào?</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Trong tim tôi, người bạn ơi.</t>
+          <t>Trong tim ta, người bạn ơi.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Có lẽ bạn đã nghe câu chuyện về Grand Commander rồi chứ?</t>
+          <t>Có lẽ cậu đã nghe qua câu chuyện về Đại Tư Lệnh?</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đại Tư Lệnh? Đó là ai?</t>
+          <t>Tổng Tư Lệnh? Đó là ai thế?</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Tôi nghĩ cậu nên đến thăm Đại Tư Lệnh.</t>
+          <t>Ta nghĩ cậu nên đến gặp Đại Chỉ Huy một chuyến.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Dù mong được gặp lại anh, nhưng ta phải vung kiếm trong tim và tiếp tục dẫn dắt cuộc chiến của riêng mình.</t>
+          <t>Dù ta mong được gặp lại hắn, nhưng ta phải vung kiếm trong tim và tiếp tục dẫn dắt cuộc chiến của riêng mình.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Joljodra chỉ cho bạn hướng về phía Grand Commander.</t>
+          <t>Joljodra chỉ tay về phía Đại Tư Lệnh cho cậu.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ta đã nghe câu chuyện của ngươi từ Đại Chỉ huy. Có vẻ thanh kiếm trong tim ngươi cũng sắc bén như thanh kiếm của ta.</t>
+          <t>Ta đã nghe câu chuyện của ngươi từ Đại Chỉ Huy. Có vẻ thanh kiếm trong tim ngươi cũng sắc bén như của ta vậy.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Nếu muốn tiếp tục thăng tiến, tôi sẽ chỉ đường cho cậu đến gặp Đại Tư Lệnh một lần nữa.</t>
+          <t>Nếu muốn tiếp tục tiến công, ta sẽ chỉ đường cho ngươi đến Đại Chỉ Huy Trưởng một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>(Dẫn đầu cuộc tấn công.)</t>
+          <t>Tiến lên nào.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>(Nghỉ ngơi lúc này.)</t>
+          <t>(Nghỉ ngơi đã.)</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Ui da... Tay tôi. Có lẽ tuổi tác đã bắt kịp tôi rồi...</t>
+          <t>Á... Tay tôi. Tuổi tác cuối cùng cũng đuổi kịp tôi rồi...</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Nhìn kìa. Ở trên đó! Hắn không xuống được!</t>
+          <t>Nhìn kìa! Ở trên đó! Nó không xuống được!</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cứu với, cứu với!</t>
+          <t>Cứu với! Cứu tôi!</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Cảm ơn rất nhiều vì đã cứu tớ. Nếu không có cậu ở đây, có lẽ tớ đã ngã sấp mặt xuống đất rồi.</t>
+          <t>Cảm ơn cậu rất nhiều vì đã cứu tớ. Nếu không có cậu ở đây, có lẽ tớ đã ngã sấp mặt xuống đất rồi.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Cậu ổn chứ?</t>
+          <t>Cậu ổn không?</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Nguy hiểm thật đấy.</t>
+          <t>Nguy hiểm quá.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Không sao, tôi ổn mà. Miễn là máy ảnh của tôi không sao là mọi thứ đều ổn. Nó vẫn hoạt động hoàn hảo! Nhưng tay tôi... *thở dài* Còn những bức ảnh thì sao?</t>
+          <t>Không sao, tớ ổn mà. Miễn là máy ảnh của tớ không sao là mọi thứ đều ổn. Nó vẫn hoạt động tốt lắm! Nhưng tay tớ... *thở dài* Còn mấy tấm ảnh thì sao nhỉ?</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Ừ. Tớ đang làm một bộ sưu tập ảnh tên là "Ký Ức Xưa Của Jinzhou". Nói chung là trộn cả ảnh cũ và mới của thành phố lại với nhau.</t>
+          <t>Ừ. Tao đang làm một bộ sưu tập ảnh tên là "Ký ức xưa của Jinzhou". Nói chung là trộn cả ảnh cũ và mới của thành phố lại.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Tôi làm phóng viên cho tạp chí Wutherium Geographic thuộc Pioneer Association.</t>
+          <t>Tôi là phóng viên của tạp chí Wutherium Geographic, thuộc Hiệp hội Pioneer.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Nhưng tất cả đã là quá khứ rồi. Tôi già rồi và sắp nghỉ hưu...</t>
+          <t>Nhưng tất cả những điều đó đều đã là quá khứ. Ta giờ đã già và sắp về hưu...</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Tôi có thể giúp cậu một tay.</t>
+          <t>Tớ có thể giúp cậu một tay.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Thật sao? Bạn thực sự đồng ý chứ? Tôi không biết phải nói gì nữa! Tôi-tôi sẽ ghi công bạn trong tạp chí và chắc chắn sẽ trả thù lao. Xin hãy giúp tôi, bạn là hy vọng duy nhất của tôi!</t>
+          <t>Thật sao? Cậu thật lòng à? Tớ không biết phải nói gì nữa! Tớ sẽ ghi tên cậu vào tạp chí và trả tiền đầy đủ, nhất định đấy. Làm ơn đi, cậu là hy vọng duy nhất của tớ!</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Chuyện nhỏ thôi mà.</t>
+          <t>Chẳng có gì to tát cả.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Tôi nên làm thế nào?</t>
+          <t>Tôi nên làm thế nào đây?</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>À! Cầm máy ảnh của tôi đi. Chỉ cần ngắm cảnh muốn chụp rồi nhấn nút chụp, khoảnh khắc ấy sẽ được lưu giữ mãi mãi...</t>
+          <t>À! Cầm máy ảnh của ta đi. Chỉ cần ngắm cảnh muốn chụp rồi bấm nút chụp, khoảnh khắc ấy sẽ được lưu giữ mãi mãi...</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Cảnh đầu tiên là khu đất cao nơi tôi vừa đứng. Chúc may mắn và cẩn thận nhé!</t>
+          <t>Địa hình đầu tiên là chỗ cao mà tao đứng lúc nãy. Cố gắng và cẩn thận nhé!</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Đúng. Chính là cái đó!</t>
+          <t>Ừ. Chính nó đấy!</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tuyệt. Để tôi xem thử nào.</t>
+          <t>Tốt đấy. Để ta xem thử nào.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Của bạn đây.</t>
+          <t>Của cậu đây.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Để xem nào... Thật tuyệt vời! Bạn có khiếu chụp ảnh đấy chứ, phải không?</t>
+          <t>Xem này... Đẹp quá! Cậu chụp ảnh tự nhiên thật đấy nhỉ?</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Nhìn xem nước trong ao này trong suốt thế nào!</t>
+          <t>Nhìn độ trong của cái hồ này kìa!</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Tôi rất thích nơi này khi còn nhỏ. Lúc nào tôi cũng đến đây một mình để chơi.</t>
+          <t>Hồi nhỏ, mình rất thích nơi này. Lúc nào cũng tự mình đến đây chơi một mình.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Bố mẹ tôi lo lắng tôi có thể tự ý nhảy xuống bơi hoặc gì đó, nên họ đã cho tôi một chiếc máy ảnh.</t>
+          <t>Bố mẹ lo mình sẽ nhảy xuống đó bơi hay gì đó một mình, nên đã đưa cho mình một cái máy ảnh.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Bố tôi bảo nếu thấy thứ gì thích thì nên chụp ảnh lại.</t>
+          <t>Bố con bảo nếu thấy thứ gì thích thì chụp lại cho bố xem.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Thật đấy, cầm đồ đắt tiền trên tay, tôi không dám nhảy xuống nước cùng nó đâu.</t>
+          <t>À, cầm món đồ đắt tiền thế này trên tay, tôi đâu dám nhảy xuống nước chứ.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Nhưng cuối cùng tôi lại chụp được rất nhiều ảnh vì chuyện đó.</t>
+          <t>Nhưng chính vì thế mà tôi lại chụp được kha khá ảnh đấy.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Từ đó tôi bắt đầu học nhiếp ảnh, ngày càng tiến bộ. Và Jinzhou cũng dần phát triển theo.</t>
+          <t>Đó là cách tôi bắt đầu học nhiếp ảnh, và ngày càng tiến bộ. Cũng từ đó, Jinzhou bắt đầu phát triển thịnh vượng.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Đường phố đông đúc hơn, cửa hàng nhiều hơn, và kinh doanh thịnh vượng hơn. Đó là một thời kỳ tốt đẹp.</t>
+          <t>Lúc đó trên đường phố đông người hơn, cửa hàng nhiều hơn, kinh doanh thịnh vượng hơn. Đó là khoảng thời gian tốt đẹp.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Được rồi, tôi nghĩ thế là đủ lẩm bẩm rồi. Xin lỗi nhé, tôi không thể ngừng nghĩ về những chuyện như thế này một khi đã bắt đầu.</t>
+          <t>Thôi được rồi, nói lẩm bẩm đủ rồi. Xin lỗi mọi người nhé, tôi mà đã nghĩ đến những chuyện này thì không thể dừng lại được.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Chúng ta nên chuyển sang cảnh tiếp theo. Và địa điểm là...</t>
+          <t>Ta nên tiếp tục đến cảnh quan tiếp theo. Nơi đó là...</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ồ! Tôi có ý này! Bạn có thích mèo không?</t>
+          <t>Ôi! Tớ có ý này! Cậu có thích mèo không?</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Xin lỗi. Tôi là người yêu chó.</t>
+          <t>Xin lỗi. Ta là người yêu chó.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Meow.</t>
+          <t>Meo.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Tuyệt vời! Những chú mèo con nhỏ, mềm mại và đáng yêu. Ai cũng thích chúng!</t>
+          <t>Tuyệt thật! Mấy em mèo nhỏ, mềm mại và đáng yêu. Ai cũng thích chúng!</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Haha, chó cũng dễ thương đấy chứ! Nhưng...</t>
+          <t>Haha, chó cũng dễ thương lắm! Nhưng mà...</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Bạn đúng là biết cách làm mèo!</t>
+          <t>Cậu đúng là biết làm mèo ghê!</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Tiếp theo, tôi muốn bạn chụp ảnh một con mèo. Được chứ?</t>
+          <t>Tiếp theo, tớ muốn cậu chụp ảnh một con mèo nhé. Được không?</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Không vấn đề gì.</t>
+          <t>Không thành vấn đề.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Tôi sẽ đánh dấu vị trí cho cậu. Đi thôi nào.</t>
+          <t>Tao sẽ đánh dấu vị trí cho mày. Đi thôi.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Ngay đằng kia. Thấy mấy con mèo không, bạn có thể đến vuốt ve chúng nếu muốn.</t>
+          <t>Chỗ đó đấy. Thấy mấy con mèo kia không, cậu có thể lại vuốt ve chúng nếu muốn.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Well? Để xem chú mèo lông xù đáng yêu kia đi.</t>
+          <t>Sao nào? Để xem con thú lông lá đáng yêu kia nào.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Của bạn đây.</t>
+          <t>Của cậu đây.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Bức ảnh thật đẹp. Nhìn nó ngủ trông thật thư thái. Trông thật thoải mái.</t>
+          <t>Bức ảnh đẹp thật. Nhìn nó ngủ say sưa thế này, thoải mái quá đi.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Trước đây cũng có vài chú mèo con quanh đây. Tôi thường đến thăm chúng mỗi khi đi công tác về.</t>
+          <t>Chỗ này trước kia cũng có vài chú mèo con. Mỗi lần đi công tác về, tôi lại ghé thăm chúng.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Và có một con tam thể y như thế này. Nó đã trở nên rất thân thiết với tôi.</t>
+          <t>Và đã từng có một con mèo tam thể giống hệt thế này. Nó rất thân với ta.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Tôi thường đến thăm cậu ấy, mang đồ ăn đến, vuốt tóc cậu ấy.</t>
+          <t>Tôi thường đến thăm cậu ấy, mang đồ ăn đến, vuốt ve mái tóc của cậu ấy.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Thật tiếc khi tôi bận công việc và phải đi xa nhiều nên không thể đưa cậu ấy về nhà.</t>
+          <t>Thật tiếc khi tôi bận rộn với công việc và thường xuyên đi xa, không thể đưa cậu ấy về nhà.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Có lần, tôi đi công tác xa lâu ngày và khi trở về, tôi không thấy cậu ấy đâu cả.</t>
+          <t>Có lần, ta đi công tác xa lâu ngày và khi trở về, chẳng thấy hắn đâu cả.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Nó làm tôi hơi buồn nên tôi đã không ghé thăm một thời gian.</t>
+          <t>Nó làm mình buồn một chút nên mình đã không đến thăm một thời gian.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Rồi một ngày, tôi tình cờ đi ngang qua và thấy mấy chú mèo con này. Cũng có người đến cho ăn và chăm sóc chúng.</t>
+          <t>Rồi một hôm tình cờ đi ngang qua, tớ thấy mấy bé mèo con này. Cũng có người đến cho ăn và chăm sóc chúng nữa.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Tôi còn đi hỏi thăm khắp nơi, và thật vui khi cuối cùng mèo tam thể đã được một gia đình tốt bụng nhận nuôi.</t>
+          <t>Tôi còn đi hỏi thăm khắp nơi, và thật vui khi cuối cùng con mèo tam thể đã được một gia đình tốt bụng nhận nuôi.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>*cười khẽ* Đó là câu chuyện của tôi với mèo. Giờ chỉ còn một nơi nữa để đến thôi. Và tôi có một việc muốn nhờ cậy.</t>
+          <t>*cười* Đó là câu chuyện của ta với lũ mèo. Giờ chỉ còn một nơi nữa thôi. Và ta có một việc muốn nhờ vả.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Tôi cần chuẩn bị một chút. Gặp lại ở đó sau nhé?</t>
+          <t>Ta cần chuẩn bị một chút. Gặp nhau ở đó sau nhé?</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Bức ảnh thế nào? Cùng xem nào.</t>
+          <t>Ảnh chụp thế nào? Đưa đây xem thử nào.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Của bạn đây.</t>
+          <t>Của cậu đây.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Ôi, xin lỗi. Tôi đã nhìn chằm chằm vào nó quá lâu rồi.</t>
+          <t>Ồ, xin lỗi cậu nhé. Ta đã nhìn chằm chằm quá lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Tớ từng chụp ảnh ở đây với gia đình, giống như gia đình kia vậy.</t>
+          <t>Tao từng chụp ảnh ở đây với gia đình mình, giống như gia đình kia vậy.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Khi tôi lớn hơn, tôi đã đủ lớn để vòng tay qua vai bố mẹ trong các bức ảnh.</t>
+          <t>Lớn lên rồi, tớ đủ cao để vòng tay qua vai bố mẹ trong những bức ảnh.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Số lượng ảnh gia đình giảm đi sau khi mình rời nhà đi làm. Giờ thì chúng chẳng còn ở đây nữa, nhưng...</t>
+          <t>Số lượng ảnh gia đình giảm dần sau khi tôi rời nhà để đi làm. Giờ thì chẳng còn tấm nào ở đây nữa, nhưng...</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Chụp thêm một bức ảnh ở đây, cùng một chỗ, cũng coi như báo với họ là mình vẫn ổn, phải không?</t>
+          <t>Chụp thêm một tấm ở chỗ này nữa, cũng coi như báo với họ là mình vẫn ổn, phải không?</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Ừ. Hôm nay cậu đã giúp mình rất nhiều. Nếu không có cậu, mình khó mà thực hiện được ước mơ ghi lại những khoảnh khắc ở Jinzhou!</t>
+          <t>Ừ. Hôm nay cậu giúp tao nhiều lắm. Nếu không có cậu, chắc tao khó mà hoàn thành được ước mơ lưu giữ lại những khoảnh khắc ở Jinzhou!</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Rover đáng kính, luôn sẵn sàng phục vụ.</t>
+          <t>Vận Mệnh Giả đáng kính, luôn sẵn sàng phục vụ.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Hiểu rồi. Tôi mang ơn bạn!</t>
+          <t>Hiểu rồi. Ta mang ơn cậu!</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Cậu phải nhận những thứ này làm phần thưởng. Giữ luôn máy ảnh của tôi nhé.</t>
+          <t>Ngươi phải nhận những thứ này làm phần thưởng. Còn máy ảnh của ta, ngươi cũng giữ luôn đi.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Mình tin tưởng vào bạn và tài năng của bạn. À, bạn có muốn thử làm phóng viên vào thời gian rảnh không?</t>
+          <t>Ta tin tưởng vào tài năng của cậu. À, nhân tiện, cậu có muốn thử làm phóng viên trong thời gian rảnh không?</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Chixia đang nói chuyện với ai đó. Quay lại sau khi họ nói chuyện xong.</t>
+          <t>Chixia đang nói chuyện với ai đó. Quay lại sau khi họ nói chuyện xong nhé.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>*sigh*...</t>
+          <t>Thở dài...</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Ông Jingzhu à, thật đấy, ông không khỏe... Thôi quên chuyện bắt &lt;ano=TD Frequencies&gt;Echoes&lt;/ano&gt; đi, mình đến bệnh viện luôn nhé?</t>
+          <t>Ông Tinh Châu, ông không khỏe thật rồi... Thôi quên việc bắt &lt;ano=TD Frequencies&gt;Echo&lt;/ano&gt; đi, mình đến bệnh viện ngay đi ạ?</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Không đời nào! Nếu không bắt được một Echo ấn tượng, tôi sẽ lo lắng đến mức ăn không ngon, ngủ không yên.</t>
+          <t>Không đời nào! Nếu không bắt được một Echo ấn tượng, tớ sẽ lo đến mất ăn mất ngủ luôn ấy!</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ôi, thôi nào! Ở tuổi này mà còn chạy theo chúng làm gì. Sao cậu lại phải kiếm một con chứ?</t>
+          <t>Ôi, thôi nào! Ở cái tuổi này mà còn chạy theo tụi nó làm gì. Sao ông lại phải đòi một cái chứ?</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Ờm, vì người tôi thích muốn có một cái!</t>
+          <t>Ờ hừm, vì người tôi thích muốn có một cái mà!</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Người cậu thích...?</t>
+          <t>Người mà cậu thích...?</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Yes. Anh biết, ở tuổi này mà tìm kiếm tình yêu thì không bình thường, nhưng anh yêu cô ấy. Cô ấy cứ từ chối anh.</t>
+          <t>Đúng vậy. Cậu biết đấy, ở tuổi này mà tìm kiếm tình yêu thì quả là hiếm, nhưng tôi yêu cô ấy. Mà cô ấy cứ từ chối tôi mãi.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Cô ấy mê Echoes chất lượng cao, nên đó là cơ hội của tớ.</t>
+          <t>Cô ấy mê Echo hùng tráng, đó là cơ hội của tớ.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Tiếc là tôi chỉ có Hoartoise thôi. Mặt tròn, đầu tròn. Chẳng có gì ấn tượng cả.</t>
+          <t>Thật tiếc, ta chỉ có một con Hoartoise thôi. Mặt tròn, đầu tròn. Chẳng có gì ấn tượng cả.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Giá mà mình có được một Echo đạt tiêu chuẩn của cô ấy, có lẽ cô ấy sẽ cho mình một cơ hội.</t>
+          <t>Nếu kiếm được một Echo đáp ứng tiêu chuẩn của cô ấy, có lẽ cô ấy sẽ cho ta một cơ hội.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Ơ... Ông Jingzhu, ông thật sự chắc chứ? Nghe hơi kỳ cục đấy. Không phải ngày nào cũng thấy một quý cô thích Echoes đâu.</t>
+          <t>Ừ... Ông nội Jingzhu, ông thật sự chắc chứ? Nghe hơi kỳ kỳ ấy. Không phải ngày nào cũng thấy một quý cô thích Echoes đâu.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ít nhất thì đây dường như là cách duy nhất để chạm đến trái tim cô ấy.</t>
+          <t>Ít ra, có vẻ đây là cách duy nhất để chạm đến trái tim cô ấy.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Dù khó khăn đến mấy, tôi vẫn quyết tâm thử sức.</t>
+          <t>Dù cơ hội mong manh, ta vẫn quyết tâm thử sức.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Nhưng cậu đang không ở trạng thái tốt nhất. Cậu thực sự nên nghỉ ngơi đi.</t>
+          <t>Nhưng cậu đang không ở trạng thái tốt nhất. Cậu thực sự nên nghỉ ngơi cho khỏe.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Ai biết được chuyện gì sẽ xảy ra nếu bạn lại ngã xuống ngọn đồi đó...</t>
+          <t>Ai biết cậu ngã xuống sườn đồi lần nữa thì sẽ ra sao...</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Ôi, xin lỗi! Tôi không nên nói những điều như vậy!</t>
+          <t>Ôi, xin lỗi cậu! Mình không nên nói những điều như vậy!</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Dù sao thì, tôi sẽ bắt một Echo ấn tượng và chinh phục tình yêu của mình.</t>
+          <t>Dù sao thì tao cũng sẽ bắt được một con Echo thật ấn tượng và đoạt được tình yêu của mình.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ôi, ông hãy suy nghĩ lại đi, ông nội Jingzhu! Echoes vẫn sẽ ở đó để ông bắt. Khi ông hồi phục, ông có thể bắt bao nhiêu tùy thích!</t>
+          <t>Ông đừng làm vậy, ông nội Jingzhu ơi! Echo vẫn sẽ ở đó chờ ông bắt mà. Khi ông khỏe lại, ông muốn bắt bao nhiêu cũng được!</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Một khi tôi hồi phục... Nhưng này, tôi đã chán chờ đợi rồi. Khi nào mới có cơ hội khác đây?</t>
+          <t>Một khi ta hồi phục... Nhưng này nhóc, ta đã chán chờ đợi rồi. Liệu cơ hội sẽ đến lần nữa khi nào?</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Ngoài ra, Tacet Discord gần đây hoạt động rất mạnh, đây chính là thời điểm tốt nhất để thu thập những Echoes ấn tượng!</t>
+          <t>Hơn nữa, gần đây Tacet Discord hoạt động mạnh nhất, nên đây là thời điểm tốt nhất để bắt được những con Echo ấn tượng!</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Tôi không thể để vuột mất cơ hội này.</t>
+          <t>Ta không thể để cơ hội này vuột mất.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi. Thế này thì sao?</t>
+          <t>Thôi thôi, thế này thì sao?</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Tôi sẽ đi bắt Echoes cho cậu, còn cậu thì đi bệnh viện đi. Được chứ?</t>
+          <t>Tớ sẽ đi bắt Echo cho cậu, đổi lại cậu phải đến bệnh viện. Được không?</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Nhưng tôi không muốn làm phiền bạn với vấn đề của mình...</t>
+          <t>Nhưng em không muốn làm phiền anh với vấn đề của riêng mình...</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Đừng lo. Chẳng có gì phiền đâu! Rốt cuộc, chăm lo nhu cầu cư dân cũng là nhiệm vụ của một Patroller mà.</t>
+          <t>Đừng lo. Chẳng có gì phiền đâu! Rốt cuộc, phục vụ cư dân cũng là nhiệm vụ của Tuần Tra viên mà.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Ồ, không cần lo về việc trả tiền cho tôi đâu! Thực ra, tôi có một người bạn rất giỏi có thể giúp đỡ. Hay chúng ta thuê {Male=anh ấy;Female=cô ấy} giúp thay thế nhé?</t>
+          <t>Ồ, không cần lo về chuyện trả công đâu! Thật ra, tôi có một người bạn rất giỏi có thể giúp được. Hay chúng ta thuê {Male=him;Female=her} thay thế nhé?</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Thế thì được với tôi.</t>
+          <t>Với tôi thì không sao.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Xuất sắc! Để chuyện này cho tôi! Ông Jingzhu, giờ ông hãy đến bệnh viện chữa vết thương đi ạ.</t>
+          <t>Tuyệt! Để đó cho tớ! Ông nội Jingzhu, giờ ông hãy đến bệnh viện chữa vết thương đi ạ.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Ông Jingzhu, số Echoes này đủ chưa ạ?</t>
+          <t>Ông Tinh Châu, số Echo này đủ chưa ạ?</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Chuẩn luôn! Xem này, Echoes thu được trong Tacet Field này có thể kết hợp thành đội với Havoc Warrior đấy.</t>
+          <t>Chắc chắn rồi! Nhìn này? Những Echo lấy được từ Tổ Tacet này có thể lập đội cùng Havoc Warrior đấy.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Hmm... Để tôi xem nào. Bạn nói đúng đấy!</t>
+          <t>Hừm... Để ta xem thử. Cậu nói đúng đấy!</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu gặp may đấy nhỉ? Tập hợp đội Echo nhanh thế. Thường thì chúng tôi phải mất khá nhiều công sức mới lập được đội đấy.</t>
+          <t>{PlayerName}, cậu gặp may đấy nhỉ? Tập hợp đội nhanh thế. Bình thường tụi tao phải mất kha khá công sức mới lập được một đội Echo cơ.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Lập một đội Echo à?</t>
+          <t>Lập đội Echo à?</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ôi, xin lỗi nhé! Mình hăng quá quên giải thích chuyện đó rồi.</t>
+          <t>Ôi, xin lỗi nhé! Tôi hăng quá quên giải thích chuyện đó là gì rồi.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Hmm... Đợi chút. Tôi đang tìm từ ngữ thích hợp.</t>
+          <t>Hừm... Đợi chút. Tớ đang tìm từ thích hợp.</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Như bạn đã biết, mỗi Echoes đều có tần số riêng biệt. Khi tập hợp nhiều Echoes lại với nhau, điều đó giống như...</t>
+          <t>Như cậu đã biết, mỗi Echo đều có tần số riêng biệt. Khi gom vài Echo lại với nhau, nó giống như...</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Giống như có một nhóm người chơi nhiều nhạc cụ khác nhau. Hầu hết thời gian, các giai điệu xung đột và trở nên hỗn loạn.</t>
+          <t>Giống như một đám người chơi những nhạc cụ khác nhau. Phần lớn thời gian, giai điệu chẳng ăn nhập gì với nhau, chỉ toàn hỗn độn.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Nhưng đôi khi, các giai điệu hòa quyện hoàn hảo với nhau, tạo nên một bản hòa âm tuyệt đẹp!</t>
+          <t>Nhưng cũng có những lúc giai điệu hòa quyện hoàn hảo, tạo nên một bản hòa âm tuyệt đẹp!</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Thành lập đội Echo cũng đơn giản vậy thôi!</t>
+          <t>Lập đội Echo cũng đơn giản như thế thôi!</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Hy vọng là cậu hiểu được... Dù sao thì sao không thử tự mình trải nghiệm? Đó là cách nhanh nhất để hiểu rõ!</t>
+          <t>Hy vọng là cậu hiểu được... Dù sao thì, sao không thử tự mình trải nghiệm? Đó là cách nhanh nhất để hiểu thôi!</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tuyệt vời, thật sự rất tuyệt vời. Đội Echo này ấn tượng hơn nhiều so với đội của tôi ngày xưa, haha!</t>
+          <t>Làm tốt lắm, quả thực là tốt. Đội Echo này còn ấn tượng hơn cả đội của tao ngày xưa, haha!</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Được rồi, tôi cảm thấy tự tin tràn đầy rồi! Quay lại Jinzhou và khiến cô ấy phải choáng ngợp nào!</t>
+          <t>Được rồi, tao cảm thấy tự tin tràn trề rồi! Quay lại Jinzhou và khiến cô ấy phải trầm trồ nào!</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Cho tôi vài phút.</t>
+          <t>Để tao có chút thời gian.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Hehe, tớ có thể tưởng tượng ra vẻ mặt của cô ấy rồi!</t>
+          <t>Hehe, ta có thể tưởng tượng ra vẻ mặt của cô ấy rồi!</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Không vội đâu. Tớ cũng cần chuẩn bị chút nữa. Nói gì với cô ấy đây nhỉ…</t>
+          <t>Đừng vội. Tớ cũng cần chuẩn bị chút nữa. Nói gì với cô ấy đây…</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Nhà cô ấy ở đằng kia. Tôi đã đi qua con đường đó nhiều lần rồi, không thể nhầm được đâu.</t>
+          <t>Nhà cô ấy ở đằng kia. Tôi đã đi qua con đường ấy bao lần, không thể nhầm được.</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Trước khi tôi đến gõ cửa cô ấy, có một việc tôi cần nhờ cậu giúp.</t>
+          <t>Trước khi ta đến gõ cửa cô ấy, có một việc ta phải nhờ ngươi giúp.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Hừm, tôi đã chuẩn bị vài câu mở đầu và cần sự trợ giúp của bạn để chuyển lời.</t>
+          <t>Ờ hừm, tôi đã chuẩn bị vài lời mở đầu và cần cậu giúp tôi truyền tải chúng.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>À, chỉ là vài lời lẽ khéo léo thôi, chắc chắn sẽ có tác dụng.</t>
+          <t>À, chỉ là vài lời lẽ khéo léo thôi, tớ tin chắc nó sẽ hiệu quả ngay.</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Em có biết điều gì ngọt ngào hơn bất kỳ loài hoa nào không? Không phải ánh sáng của Waterlamp, cũng chẳng phải hương thơm của Iris, mà chính là sự nở rộ của tình yêu chúng ta hòa quyện hoàn hảo!</t>
+          <t>Cậu có biết thứ gì ngọt ngào hơn bất kỳ loài hoa nào không? Không phải ánh sáng của Waterlamp, cũng chẳng phải hương thơm của Iris, mà chính là bông hoa tình yêu của chúng ta nở rộ theo khúc nhạc hoàn hảo!</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Bạn có biết điều gì tồn tại mãi mãi trong Wuthering Waves không? Không phải những nền văn minh phù du, cũng không phải truyền thuyết về Tacet Discord, mà là tình yêu bất diệt của tôi dành cho bạn, mãi mãi!</t>
+          <t>Cậu có biết điều gì tồn tại mãi mãi trong Wuthering Waves không? Không phải những nền văn minh phù du, cũng chẳng phải huyền tích của Tacet Discord, mà chính là tình yêu bất diệt ta dành cho cậu, vĩnh viễn!</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Ừm... Ông Jingzhu, đây là những gì thế ạ?</t>
+          <t>Ừm... Ông nội Jingzhu, đây là gì thế ạ?</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Tin Nhắn Tình Yêu Phổ Biến ở Huanglong&lt;/i&gt;! Ừm, tôi biết có vẻ hơi kỳ lạ khi một người ở tuổi tôi lại nói những điều như vậy...</t>
+          <t>&lt;i&gt;Những Lời Tình Yêu Phổ Biến ở Huanglong&lt;/i&gt;! Ừm, biết là hơi kỳ cục khi một người ở tuổi tôi lại nói những điều như thế...</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Nhưng miễn là tôi có thể chiếm được trái tim cô ấy, tôi có thể gác lại lòng tự trọng của mình.</t>
+          <t>Miễn là ta có thể chiếm được trái tim nàng, ta sẵn sàng gạt bỏ cả lòng tự trọng.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tôi trông cậy vào cậu. Sau khi tôi nói xong lời thoại của mình, cậu sẽ nối tiếp để tạo không khí hoàn hảo.</t>
+          <t>Ta trông cậy vào cậu đấy. Sau khi ta nói xong lời của mình, cậu sẽ tiếp lời để tạo không khí hoàn hảo.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Được rồi, đồng ý.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>{PlayerName}, tôi không ngờ cậu còn giúp ích hơn cả tôi! Giỏi lắm!</t>
+          <t>{PlayerName}, ta không ngờ cậu còn giúp ích hơn cả ta nữa! Giỏi lắm!</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Tất nhiên, tôi sẽ không tiếc phần thưởng xứng đáng cho công sức của cậu.</t>
+          <t>Tất nhiên, ta sẽ không hà tiện đâu. Công sức của các ngươi sẽ được đền đáp xứng đáng.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đó là cô ấy, Linghan, v-vợ tôi... vợ tương lai của tôi.</t>
+          <t>Đó là nàng, Linghan, v-vợ yêu dấu của ta... vợ tương lai của ta.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Đó là hoa Noctemint, loài hoa cô ấy yêu thích.</t>
+          <t>Đó là hoa Noctemint, loài hoa cô ấy yêu thích nhất.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Tôi sắp hỏi cô ấy: "Em có chấp nhận Noctemint này và cùng tôi bước vào hành trình cả đời không?"</t>
+          <t>Ta sắp hỏi cô ấy: "Em có nhận lấy Noctemint này và cùng ta bước vào hành trình cả đời không?"</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nhưng than ôi, nỗ lực của tôi dường như vẫn chưa đủ... Tôi thật sự hy vọng lần này cô ấy sẽ thích món Noctemint này.</t>
+          <t>Nhưng than ôi, nỗ lực của ta dường như vẫn chưa đủ... Thật lòng mong lần này nàng sẽ thích loài Noctemint này.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Có lẽ, với lời mở đầu chuẩn bị kỹ lưỡng cùng những Echoes hùng vĩ mà cậu thu thập được, cô ấy cuối cùng cũng sẽ chấp nhận tình cảm của tôi.</t>
+          <t>Có lẽ, với lời mở đầu mà ta đã chuẩn bị kỹ lưỡng cùng những Echo hùng vĩ mà ngươi thu thập được, nàng cuối cùng cũng sẽ chấp nhận tình yêu của ta.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Bạn còn nhớ câu mở đầu không? Tôi sẽ nói trước, rồi bạn nối tiếp nhé! Nhớ tạo không khí đấy!</t>
+          <t>Cậu còn nhớ lời mở đầu không? Để tớ nói trước, rồi cậu nối tiếp nhé! Nhớ tạo không khí đấy!</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thì, nhưng...</t>
+          <t>Thôi, nhưng mà...</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Sẵn sàng rồi!</t>
+          <t>Sẵn sàng mọi lúc!</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Được rồi, không còn thời gian để lãng phí nữa. Tôi phải hành động ngay thôi!</t>
+          <t>Được rồi, không thể chần chừ nữa. Tôi phải hành động thôi!</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Ôi, {PlayerName}, nhiệt huyết của cậu thật truyền cảm! Tớ cũng hứng khởi theo luôn!</t>
+          <t>Ôi, {PlayerName}, nhiệt huyết của mày lây quá! Tao cũng thấy hừng hực lên đây này!</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Không phải ánh sáng của Waterlamp!</t>
+          <t>Không phải ánh sáng của Đèn Nước đâu!</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Cũng chẳng phải hương Iris.</t>
+          <t>Cũng không phải là hương thơm của Iris.</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Nhưng đóa hoa tình yêu chúng ta đã hòa tấu hoàn hảo!</t>
+          <t>Nhưng đó là khúc hoa tình yêu hoàn hảo của chúng ta!</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Good! Hãy tấn công khi còn nóng!</t>
+          <t>Tốt! Phải chớp lấy thời cơ khi còn nóng đấy!</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Cậu có biết điều gì tồn tại mãi mãi trong Wuthering Waves không?</t>
+          <t>Con có biết thứ gì tồn tại mãi mãi ở Wuthering Waves không?</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Không phải những nền văn minh phù du!</t>
+          <t>Không phải những nền văn minh thoáng qua!</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Truyền thuyết về Nor Tacet Discords.</t>
+          <t>Cũng không phải là truyền thuyết về Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nhưng tình yêu bất diệt của anh dành cho em, mãi mãi không đổi!</t>
+          <t>Nhưng tình yêu bất diệt của anh dành cho em sẽ mãi mãi không đổi!</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Xong chưa? Xin phép tôi đi trước.</t>
+          <t>Xong chưa? Xin lỗi cho mình đi qua nhé.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Khoan! Tớ có điều bất ngờ cho cậu!</t>
+          <t>Đợi đã! Tôi có một bất ngờ dành cho anh!</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Nhanh lên! Cho cô ấy xem những Echoes hùng vĩ kia đi!</t>
+          <t>Nhanh nào! Cho cô ấy xem những Âm Hưởng huy hoàng đó đi!</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nhìn này! Những Echoes này ấn tượng chứ? Hai đứa trẻ này đã giúp tôi bắt được chúng đấy.</t>
+          <t>Nhìn này! Những Echo này đẹp chứ? Hai đứa nhỏ này đã giúp ta bắt được chúng đấy.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Nói về Echoes thì đó chính là chuyên môn của tôi.</t>
+          <t>Nói về Echo, đó là chuyên môn của tôi.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Điều quan trọng nhất là tìm được Echo đồng điệu với bạn và nuôi dưỡng nó một cách khôn ngoan. Hãy luôn nhớ, đừng để vẻ ngoài đánh lừa quyết định của bạn!</t>
+          <t>Điều quan trọng nhất là tìm được Echo cộng hưởng với mình và nuôi dưỡng nó một cách khôn ngoan. Nhớ kỹ nhé, đừng để vẻ bề ngoài đánh lừa quyết định của con!</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Ừ, ừ. Vậy cậu có muốn nhận Noctemint này không?</t>
+          <t>Ừ, ừ. Vậy, cậu có muốn nhận lấy Noctemint này không?</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Không, cảm ơn. Tôi không quan tâm. Tôi thà phơi nắng và nhâm nhi hạt dưa một mình.</t>
+          <t>Không, cảm ơn. Tao không hứng thú đâu. Thà nằm phơi nắng nhấm nháp mấy hạt dưa còn hơn.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Bà Linghan đã từ chối cậu ấy rồi, phải không?</t>
+          <t>Bà Linghan từ chối cậu ta rồi đúng không?</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Đích thị là từ chối rồi.</t>
+          <t>Chắc chắn là bị từ chối rồi.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Ông Jingzhu chắc hẳn đang rất buồn.</t>
+          <t>Ông Tinh Châu chắc đang rất buồn.</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Ừ, hơi buồn một chút. Mình cũng thấy hơi thất vọng...</t>
+          <t>Ừ, hơi buồn thật đấy. Tao cũng thấy hơi chán chút...</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tôi không hề nản chí, dù chỉ một chút!</t>
+          <t>Tao không hề nản chí, một chút cũng không!</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tôi đã suy ngẫm về lời của Linghan, và mọi chuyện đã trở nên rõ ràng với tôi.</t>
+          <t>Tớ đã suy ngẫm về lời của Linghan, và mọi thứ đã trở nên rõ ràng với tớ rồi.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Cô ấy không hề từ chối tôi. Cô ấy chỉ nhắc nhở tôi phải nuôi dưỡng Echoes một cách cẩn thận.</t>
+          <t>Cô ấy không hề từ chối ta. Cô ấy chỉ muốn ta nuôi dưỡng những Âm Vang ấy thật cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Đó là cách cô ấy dẫn dắt tôi tiến về phía trước. Hahaha, cô ấy thật sự quan tâm đến tôi!</t>
+          <t>Đó là cách cô ấy dẫn dắt tôi tiến lên. Hahaha, cô ấy thật sự quan tâm đến tôi!</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>...Bắt đầu tự hỏi không biết ông nội Jingzhu có bị va đầu không.</t>
+          <t>...Bắt đầu nghi ngờ ông Jingzhu có bị va đầu không rồi.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Đi nào, các bạn trẻ! Không còn thời gian để lãng phí đâu. Chúng ta sẽ rời thành phố để thu thập những vật liệu cần thiết...</t>
+          <t>Nhanh lên nào, các bạn trẻ! Không có thời gian để lãng phí đâu. Chúng ta phải rời thành phố để thu thập nguyên liệu cần thiết...</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Ôi, xin lỗi nhé. Tôi hăng quá nên quên mất thời gian. Chắc hẳn cậu đã mệt lắm rồi. Để hôm khác nhé.</t>
+          <t>Ôi, xin lỗi nhé. Tôi hăng quá nên quên mất thời gian. Chắc cậu mệt lắm rồi. Hôm khác làm tiếp nhé.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>À, suýt quên. Đây là khoản bồi thường của cậu. Xin hãy nhận lấy.</t>
+          <t>À, suýt quên mất. Đây là khoản bồi thường của cậu. Xin hãy nhận lấy.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Nếu anh cứ khăng khăng thế.</t>
+          <t>Nếu ngươi nhất quyết vậy.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Thật sao? Cứ thế nhận luôn à?</t>
+          <t>Thật sao? Cứ thế lấy luôn à?</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tốt lắm! Lần sau tôi nhờ giúp, tôi cũng sẽ trả công xứng đáng. Đó là cách tạo dựng mối quan hệ, phải không?</t>
+          <t>Tốt! Lần sau tôi nhờ giúp việc, tôi sẽ trả công hậu hĩnh. Đó mới là cách xây dựng mối quan hệ phải không?</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Cầm lấy đi, nhóc. Cậu xứng đáng nhận nó. Lần sau tôi nhờ cậu giúp, tôi cũng sẽ trả công xứng đáng. Đó là cách tạo dựng mối quan hệ, phải không?</t>
+          <t>Cầm lấy đi, nhóc. Cậu xứng đáng mà. Lần sau tao nhờ giúp, tao sẽ trả hậu hĩnh. Đó mới là cách xây dựng mối quan hệ, phải không?</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Hôm nay cả hai đã làm việc vất vả rồi. Mau về nghỉ ngơi đi nhé! Cảm ơn các cậu!</t>
+          <t>Hôm nay cả hai cậu đã làm việc rất vất vả rồi. Mau về nghỉ ngơi đi nhé! Cảm ơn các cậu!</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Này, Rover! Còn nhớ ông Jingzhu không?</t>
+          <t>Này, Vận Mệnh Giả! Còn nhớ ông Jingzhu không?</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Đúng rồi, người đã nói câu "tình-yêu-bất-diệt" ấy.</t>
+          <t>Ừ, người nói câu "tình-yêu-bất-diệt" đó.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Người đã nói câu "tình-yêu-bất-diệt" ấy. Gợi nhớ gì chưa?</t>
+          <t>Kẻ từng nói câu "tình-yêu-bất-diệt" ấy. Giờ nhớ ra chưa?</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>À, tôi vừa gặp cậu ấy lúc nãy, và cậu ấy lại cần chúng ta giúp lấy Echoes. Thế nên mới gọi đấy.</t>
+          <t>Thế nên, tôi mới gặp hắn lúc nãy, và hắn cần chúng ta giúp lấy lại Echoes. Thế nên mới gọi cậu.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Được thôi, sao lại không?</t>
+          <t>Được thôi, tại sao không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Tuyệt! Vậy thì chúng ta sẽ gặp nhau gần khu huấn luyện nhé.</t>
+          <t>Tuyệt! Vậy thì gặp cậu ở khu tập luyện nhé.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Không sao đâu. Ghé qua khu huấn luyện khi cậu rảnh nhé.</t>
+          <t>Không sao đâu. Khi nào rảnh thì ghé qua khu huấn luyện nhé.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Giờ mọi người đã tới đông đủ, ông Jingzhu à, kế hoạch là gì ạ?</t>
+          <t>Giờ mọi người đều có mặt rồi, ông Jingzhu, kế hoạch là gì?</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Kể từ lần chia tay trước, tôi đã suy ngẫm về lời của Linh Hàn, và chúng đã cho tôi một góc nhìn mới!</t>
+          <t>Kể từ lần chia tay trước, ta đã suy ngẫm rất nhiều về lời của Linghan, và chúng đã cho ta một góc nhìn mới!</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Cô ấy tin rằng Lưỡi Hái chỉ hào nhoáng bề ngoài, nhưng thiếu thực tế và sắc bén khi làm vũ khí.</t>
+          <t>Con bé cho rằng Scythe chỉ đẹp mã ngoài mặt, chứ thiếu thực dụng và sắc bén khi làm vũ khí.</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Nếu tớ mài sắc những lưỡi hái này đến độ bén như lưỡi dao, Linghan chắc chắn sẽ vui vẻ nhận Noctemint của tớ.</t>
+          <t>Chắc chắn nếu tớ mài mấy lưỡi hái này sắc như lưỡi dao, Linghan sẽ vui vẻ nhận Noctemint của tớ thôi.</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Lần này anh chắc chứ?</t>
+          <t>Lần này chắc chắn rồi chứ?</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Có công mài sắt có ngày nên kim. Chỉ cần thử là biết ngay thôi.</t>
+          <t>Càng luyện tập càng tiến bộ. Chỉ cần thử là ta sẽ biết câu trả lời.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Hừm, cuộc sống vốn dĩ đầy bất trắc. Nếu lần này thất bại, vẫn còn cơ hội khác mà!</t>
+          <t>Ừm, cuộc sống đầy bất trắc mà. Nếu lần này thất bại, vẫn còn cơ hội khác chứ!</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Được rồi, giờ hãy mài mấy lưỡi hái khổng lồ này thôi!</t>
+          <t>Được rồi, giờ thì mài mấy lưỡi hái khổng lồ này thôi!</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Ừm... Nói đến bãi huấn luyện Echo thì...</t>
+          <t>Ừm... Nói đến khu huấn luyện Echo...</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Ừm, nhưng hôm nay có {PlayerName} bên cạnh, chắc sẽ không căng thẳng lắm nhỉ?</t>
+          <t>Ừm, nhưng hôm nay có {PlayerName} ở đây cùng bọn mình, chắc sẽ đỡ căng thẳng hơn nhiều nhỉ?</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Nhát gan không phải là tính cách của một Patroller! Hãy theo tôi. Đi thôi!</t>
+          <t>Nhát gan không phải là tính cách của một Tuần Tra Viên! Theo ta nào. Lên đường thôi!</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Ta nghe đồn Yhan đã trở thành một người hướng dẫn khá nghiêm khắc. Ngươi nên cẩn thận đấy.</t>
+          <t>Tao nghe đồn Yhan giờ đã trở thành một huấn luyện viên nghiêm khắc lắm. Cậu nên cẩn thận đấy.</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Trong đó có khá nhiều đàn em từng bị tôi "dạy dỗ" đấy, haha! Vậy nên tôi sẽ không tham gia cùng các cậu để khỏi làm tụi nó nản chí.</t>
+          <t>Trong đó có mấy đứa hậu bối từng bị tớ "dạy dỗ" thẳng tay đấy, haha! Thôi, tớ không tham gia cùng cậu nữa, để chúng nó còn phấn chấn chút.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Chúng ta đã đến rồi. Vào đi nào. Wish you good luck!</t>
+          <t>Đến nơi rồi. Vào đi. Chúc ngươi may mắn!</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Cuối cùng cũng thuyết phục được ông Jingzhu đi bệnh viện... Trời đã tối rồi. {PlayerName} chắc cũng sắp đến nơi...</t>
+          <t>Cuối cùng cũng thuyết phục được ông Jingzhu đi bệnh viện rồi... Trễ quá rồi. {PlayerName} chắc cũng sắp đến nơi rồi...</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tôi đến rồi.</t>
+          <t>Ta đến rồi.</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Ôi trời, cậu làm tôi giật mình! Cậu đến đây từ lúc nào thế?</t>
+          <t>Ôi trời, cậu làm tớ giật cả mình! Cậu đến từ lúc nào thế?</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Khi bắt đầu cuộc trò chuyện.</t>
+          <t>Khi cuộc trò chuyện bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Vậy anh nghĩ sao?</t>
+          <t>Vậy cậu nghĩ sao?</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Miễn là anh trả tiền.</t>
+          <t>Miễn là cậu chịu trả tiền.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Tôi hơi tò mò.</t>
+          <t>Ta hơi tò mò một chút.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Tuyệt vời, vừa giúp ông Jingzhu vừa kiếm thêm chút tiền. Một mũi tên trúng hai đích luôn nhỉ?</t>
+          <t>Tuyệt, vừa giúp ông Jingzhu lại còn kiếm thêm chút tiền nữa. Một mũi tên trúng hai đích, phải không?</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Thật lòng mà nói, tôi cũng rất tò mò. Một bà cụ mà lại mê Echoes đến thế thì đúng là có gì đó không ổn!</t>
+          <t>Thật lòng mà nói, tớ cũng tò mò lắm. Một bà già mà lại mê Echoes đến thế, sao mà hợp lý được?</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Và tại sao ông nội Jingzhu lại cứng đầu thế nhỉ...</t>
+          <t>Sao ông nội Jingzhu lại cứng đầu thế nhỉ...</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Có lẽ ta sẽ có câu trả lời sau khi thu được mấy Echoes đó.</t>
+          <t>Biết đâu mình sẽ có câu trả lời sau khi bắt được mấy con Echo đó.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Được rồi, chuẩn bị xong xuôi và lên đường thôi!</t>
+          <t>Được thôi, chuẩn bị xong và lên đường nào!</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Tôi muốn luyện tập Echoes.</t>
+          <t>Tao muốn luyện tập Echoes.</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Tôi hiểu rồi. Hãy đi theo tôi. Hãy chọn một chương trình huấn luyện phù hợp với trình độ hiện tại của bạn.</t>
+          <t>Ra là vậy. Đi theo ta. Hãy chọn chương trình huấn luyện phù hợp với trình độ hiện tại của cậu.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Hello, lại gặp nhau rồi. Lần này bạn đến vì chuyện gì?</t>
+          <t>Xin chào, lại gặp nhau rồi. Lần này cậu đến đây có việc gì thế?</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Chỉ là lời cảnh báo thôi. Đừng để sự tự tin thái quá che mờ lý trí khi lựa chọn. Khôn ngoan là không nên ôm đồm quá sức.</t>
+          <t>Chỉ là lời cảnh báo thôi. Đừng để tự tin quá mức che mờ lý trí khi lựa chọn. Khôn ngoan là đừng ôm đồm quá sức mình.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Nếu không, ngươi có thể sẽ phải khóc đấy.</t>
+          <t>Nếu không, cậu có thể sẽ phải khóc đấy.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Not bad. Vượt xa mong đợi của tôi.</t>
+          <t>Không tồi. Vượt xa mong đợi của tao.</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu chưa bao giờ làm tôi thất vọng.</t>
+          <t>{PlayerName}, cậu luôn khiến tớ phải ngạc nhiên.</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Đừng ngần ngại đến gặp tôi nếu bạn cần giúp đỡ. Tôi rất sẵn lòng cung cấp các buổi huấn luyện ở nhiều cấp độ khác nhau cho những người nhiệt huyết như bạn.</t>
+          <t>Nếu cần giúp đỡ gì, cứ đến tìm ta nhé. Ta rất sẵn lòng hướng dẫn những người nhiệt huyết như các ngươi ở nhiều trình độ khác nhau.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tôi không ngờ chúng ta lại vượt qua khóa huấn luyện nhanh đến vậy! {PlayerName}, cậu quả thật xứng với danh tiếng của mình!</t>
+          <t>Tôi không ngờ chúng ta lại vượt qua khóa huấn luyện nhanh đến thế! {PlayerName}, cậu quả là xứng với danh tiếng của mình!</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Quay lại sớm thế?</t>
+          <t>Quay lại nhanh thế?</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Yhan quả là một nhân vật đáng gờm. Vượt qua buổi huấn luyện của anh ấy thật đáng khen ngợi.</t>
+          <t>Yhan quả là một nhân vật đáng gờm. Vượt qua buổi huấn luyện của hắn một cách dễ dàng như vậy, thật đáng khen.</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Ta không hề nghi ngờ rằng thế giới này sẽ sớm nằm dưới chân các cậu, những người trẻ tuổi!</t>
+          <t>Ta không nghi ngờ gì rằng thế giới này sẽ sớm nằm trong tay các cháu!</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Haha, đủ nói chuyện rồi. Bây giờ hãy bắt tay vào việc chính thôi. Lưỡi hái của Havoc Warrior đang chờ chúng ta mài giũa!</t>
+          <t>Haha, nói đủ rồi. Bắt tay vào việc thôi. Lưỡi hái của Havoc Warrior đang đợi chúng ta mài sắc đây!</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Ồ! Bây giờ còn ấn tượng hơn! Nhìn mấy lưỡi hái kia kìa—đáng sợ thật đấy!</t>
+          <t>Ôi! Bây giờ trông còn ấn tượng hơn nữa! Nhìn đôi lưỡi hái kia đi—đáng sợ thật đấy!</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Dù tràn đầy sức trẻ, nhưng trải qua lại khóa huấn luyện của Yhan trong thời gian ngắn như vậy có lẽ vẫn là một thử thách không nhỏ. Có lẽ, chúng ta có thể...</t>
+          <t>Dù tràn đầy sức trẻ, nhưng chịu đựng lại khóa huấn luyện của Yhan trong thời gian ngắn như vậy có lẽ vẫn là một thử thách không nhỏ. Hay là... chúng ta thử...</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Giọng nói này... Tôi biết là ông rồi, ông Jingzhu.</t>
+          <t>Giọng nói này... Ta biết mà, ông Jingzhu.</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Giáo-giáo viên Yhan?</t>
+          <t>Th- Thầy Yhan ạ?</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>À, cậu vẫn nhận ra gương mặt này đấy à, Yhan.</t>
+          <t>À, cậu vẫn nhận ra gương mặt già nua này à, Yhan.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Chúng ta đã làm vậy từ rất lâu rồi.</t>
+          <t>Chúng tôi làm vậy và làm lâu lắm rồi.</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Thời còn là Midnight Rangers, ông Jingzhu đã nhận được sự kính trọng tuyệt đối từ tôi.</t>
+          <t>Thời còn Midnight Rangers, ông Jingzhu là người mà ta kính trọng nhất.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Lâu rồi mới gặp lại. Ông Jingzhu. Ông vẫn trông khỏe mạnh... dù chân có vẻ không còn nhanh nhẹn như xưa?</t>
+          <t>Lâu rồi không gặp, ông Jingzhu. Trông ông vẫn khỏe mạnh... dù chân có vẻ không còn nhanh nhẹn như xưa nhỉ?</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Ờm, chỉ là tai nạn nhỏ thôi. Tôi già rồi mà. Trượt chân khi leo núi. Không có gì phải lo đâu!</t>
+          <t>Ừm, chỉ là tai nạn nhỏ thôi. Tôi già rồi mà, trượt chân khi leo núi. Không có gì phải lo cả!</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Tôi đang nghỉ ngơi và sẽ sớm hồi phục.</t>
+          <t>Tớ đang nghỉ ngơi và sẽ sớm hồi phục thôi.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Vết thương của cậu có vẻ đã lành rồi, nhưng đừng coi nhẹ việc nghỉ ngơi đấy.</t>
+          <t>Vết thương của bạn có vẻ đã lành tốt, nhưng đừng coi nhẹ việc nghỉ ngơi đấy.</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Cháu vẫn lắm lời như mọi khi nhỉ. Ngày xưa, chúng ta chịu đựng còn khổ hơn thế mà vẫn chiến đấu anh dũng. Nhớ chưa?</t>
+          <t>Mày vẫn lắm lời như xưa đấy, nhóc. Ngày xưa chúng tao còn chịu đựng khổ sở hơn thế này nhiều, mà vẫn chiến đấu anh dũng. Nhớ không?</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Nhưng cô đã nghỉ hưu lâu rồi mà...</t>
+          <t>Nhưng cậu đã nghỉ hưu lâu rồi mà...</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Và đây là Huấn luyện viên trưởng Yhan. Ông vẫn khỏe chứ?</t>
+          <t>Và đây là Huấn luyện viên trưởng Yhan. Chắc hẳn ông vẫn khỏe mạnh, phải không?</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Ta chỉ đang hoàn thành nhiệm vụ của mình. Còn những đồng đội cũ của ngươi thì sao?</t>
+          <t>Ta chỉ đang làm nhiệm vụ của mình thôi. Còn những đồng đội cũ của ngươi thì sao?</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Ngoại trừ Đội trưởng và tôi, tất cả họ đều... À thôi. Hãy tập trung vào những chủ đề vui vẻ hơn trong lần hội ngộ hiếm hoi này.</t>
+          <t>Ngoại trừ đội trưởng và ta, tất cả bọn họ đều... À thôi, không nhắc nữa. Nhân dịp hiếm hoi sum vầy, hãy nói chuyện vui vẻ thôi.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Quá khứ là quá khứ thôi. Khi cậu đến tuổi của tôi, cậu sẽ nhận ra rằng hiện tại mới là điều quan trọng nhất trong cuộc sống!</t>
+          <t>Quá khứ là quá khứ. Đến tuổi ta rồi, cậu sẽ hiểu rằng khoảnh khắc hiện tại mới là điều quan trọng nhất trong đời!</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Sống trọn từng khoảnh khắc và trân trọng mỗi ngày trôi qua. Đó là cách chúng ta tưởng nhớ sự hy sinh của đồng đội.</t>
+          <t>Hãy sống trọn từng khoảnh khắc và trân trọng mỗi ngày trôi qua. Đó mới là cách chúng ta tri ân sự hy sinh của đồng đội.</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Đúng vậy, ông Jingzhu. Hiện tại đòi hỏi chúng ta phải tập trung toàn lực.</t>
+          <t>Đúng vậy, ông Jingzhu à. Hiện tại mới là điều quan trọng nhất.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Đúng vậy, vậy thì hãy nói về hiện tại. Cậu biết tôi cần gì bây giờ. Cậu có sẵn lòng giúp không?</t>
+          <t>Đúng thế, giờ hãy nói về hiện tại. Cậu biết ta cần gì rồi đấy. Cậu có sẵn lòng giúp không?</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Ông Jingzhu vẫn tràn đầy khí thế như mọi khi nhỉ.</t>
+          <t>Anh Jingzhu vẫn tràn đầy năng lượng như mọi khi nhỉ.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Haha, tôi thật sự rất vinh hạnh.</t>
+          <t>Haha, thật lòng là ta rất lấy làm vinh hạnh.</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Những thứ này đủ cho nhu cầu của cậu rồi. Cầm lấy đi.</t>
+          <t>Những thứ này chắc là đủ cho cậu rồi. Cầm lấy đi.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Tuyệt, cảm ơn nhé.</t>
+          <t>Tốt rồi, cảm ơn.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Người Hướng Dẫn Yhan không độc ác như lời đồn đến thế.</t>
+          <t>Huấn luyện viên Yhan có vẻ không độc ác như lời đồn chút nào.</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Tớ vẫn còn ngạc nhiên khi biết ông Jingzhu ngày xưa từng là Midnight Ranger.</t>
+          <t>Tao vẫn còn ngạc nhiên khi biết ông Jingzhu ngày xưa từng là Midnight Ranger.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Hừm, tôi quen với việc sống lặng lẽ thôi. Chờ thời cơ gây ấn tượng với Linghan.</t>
+          <t>Hừ, ta đã quen với việc lặng lẽ chờ thời. Chỉ cần chờ cơ hội gây ấn tượng với Linghan thôi.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Làm cô ấy phải lòng tôi chỉ bằng một phát bắn!</t>
+          <t>Chỉ một phát bắn thôi, phải khiến cô ấy phải lòng ta!</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Với vẻ ngoài quyến rũ tự nhiên cùng lưỡi hái đã tôi luyện hoàn hảo, lần này tôi tin chắc sẽ chinh phục được trái tim của Linghan và khiến cô chấp nhận Noctemint của tôi!</t>
+          <t>Với sự quyến rũ tự nhiên cùng lưỡi hái đã tôi luyện hoàn hảo này, lần này tôi tin chắc sẽ chinh phục được trái tim Linghan và khiến nàng chấp nhận Noctemint của tôi!</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Anh chắc không?</t>
+          <t>Cậu chắc chắn chứ?</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Ặc, tất nhiên rồi!</t>
+          <t>Ờ hừm, chắc chắn rồi!</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Điều gì khiến ông Jingzhu tin chắc rằng sở hữu một Echo mạnh sẽ chiếm được trái tim bà Linghan?</t>
+          <t>Sao ông Jingzhu lại chắc mẩm rằng có được một Echo mạnh sẽ chiếm được trái tim bà Linghan nhỉ?</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Tớ đồng ý với cậu. Ông Jingzhu làm sao chắc chắn được là có một Echo mạnh sẽ chiếm được trái tim bà Linghan nhỉ?</t>
+          <t>Tớ đồng ý với cậu. Ông Jingzhu sao lại chắc chắn rằng có được một Echo mạnh sẽ chiếm được trái tim bà Linghan nhỉ?</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Tất nhiên, không chỉ có Echo đâu! Linghan từng chia sẻ tiêu chí về một người bạn đời lý tưởng của cô ấy.</t>
+          <t>Tất nhiên, không chỉ có Echo mà ta chuẩn bị đâu! Linghan từng chia sẻ tiêu chí về một người bạn đời lý tưởng của cô ấy.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Cậu thấy đấy? Ngoài con Echo oai phong kia ra, mọi thứ khác đều hợp với tớ hết!</t>
+          <t>Cậu thấy không? Ngoại trừ con Echo oai phong kia, mọi thứ khác đều hợp với tớ hoàn hảo!</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Sao thế? Không tin tôi à? Cũng dễ hiểu thôi, giữa chúng ta có cả một khoảng cách thế hệ mà.</t>
+          <t>Sao nhìn tao như thế? Cậu không tin tao à? Cũng phải thôi, giữa chúng ta cách nhau cả một thế hệ mà.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Nhưng khi nói đến chuyện tình cảm, nhất là với chúng ta những người lớn tuổi, tin tôi đi. Tôi hiểu mà!</t>
+          <t>Nhưng khi nói đến chuyện tình cảm, nhất là với tụi già như chúng ta, tin tao đi. Tao lo được hết!</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Được rồi, mọi thứ đã sẵn sàng. Hãy đến thăm Linghan thôi.</t>
+          <t>Được rồi, mọi thứ đã sẵn sàng. Giờ thì đến thăm Linghan thôi.</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Lại trở về đây, nơi quen thuộc này.</t>
+          <t>Lại trở về nơi quen thuộc này rồi.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Ông Jingzhu, ông đến thăm bà phải không?</t>
+          <t>Ông nội Jingzhu đến thăm bà à?</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Tớ nghe nói cậu... ừm, từ gì nhỉ? Tán tỉnh bà già à?</t>
+          <t>Tao nghe nói cậu... ừm, đang tán tỉnh bà già à?</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Ôi trời! Khoan đã, Yingying. Con còn nhỏ chưa hiểu chuyện đó đâu.</t>
+          <t>Ôi trời! Khoan đã, Yingying. Con còn nhỏ, chưa hiểu được ý nghĩa của chuyện đó đâu.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Tôi thậm chí còn học được một thuật ngữ mới! Tình yêu muộn màng!</t>
+          <t>Tôi còn học được một thuật ngữ mới! Tình yêu muộn màng!</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Dù sao thì ông cũng nên thử đi! Cháu sẽ đi báo bà là ông đến rồi!</t>
+          <t>Thôi, ông cứ làm đi! Cháu sẽ đi báo bà là ông đến rồi!</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>GRANDMA!</t>
+          <t>BÀ NỘI!</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ông Jingzhu quay lại với thêm Noctemints cho bà rồi!</t>
+          <t>Ông Tinh Châu lại mang về thêm Noctemint cho bà đây này!</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Ôi trời, trẻ con bây giờ thật là khác.</t>
+          <t>Ôi trời ơi, trẻ con bây giờ đúng là khác.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Noctemints?</t>
+          <t>Noctemint à?</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Kỳ lạ thật. Gần đây, khoảng mười quý ông đã mang Noctemint đến cho mình.</t>
+          <t>Lạ thật. Gần đây, có khoảng mười quý ông mang Noctemints đến tặng tớ.</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Và giờ tôi là người thứ mười ba... Khoan đã, những người trước đó cũng đều là tôi...</t>
+          <t>Giờ thì tớ là người thứ mười ba... Khoan đã, những người trước kia cũng đều là tớ cả...</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Còn nhớ lần trước cậu nói gì không? Không thể đánh giá một Echo chỉ qua vẻ ngoài của nó.</t>
+          <t>Nhớ lần trước cậu bảo tớ gì không? Không thể đánh giá một Echo chỉ qua vẻ ngoài đâu.</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Thật sự rất hợp lý! Vậy là mình đã mài những lưỡi hái này sắc bén hơn rồi!</t>
+          <t>Nghe hợp lý đấy chứ! Vậy là ta đã mài những lưỡi hái này sắc hơn rồi!</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Thật nhẹ cả người khi nghe vậy! Được rồi, để tôi trình bày cho cậu những gì chúng ta đã đạt được lần này!</t>
+          <t>Thật nhẹ cả người khi nghe vậy! Được rồi, để tôi trình bày cho cậu những gì chúng tôi đã đạt được lần này!</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Xin lỗi, lý do cậu đến là gì nhỉ? À, để cho ta xem Echo à?</t>
+          <t>Xin lỗi, lý do cậu đến đây là gì nhỉ? À phải, để cho tôi xem Echo à?</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>KHÔNG! Bà ơi, cậu ấy đến để tặng bà Noctemints mà!</t>
+          <t>Không! Bà ơi, cháu đến để đưa bà kẹo Noctemints mà!</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Ôi, cô gái...</t>
+          <t>Ôi, cô bé à...</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đòn hay đấy!</t>
+          <t>Động tác đẹp đấy!</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Hôm nay Yingying trông rất hoạt bát, giúp tôi rất nhiều.</t>
+          <t>Hôm nay Doanh Doanh hoạt bát hẳn ra, giúp ta rất nhiều.</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Hôm nay Yingying tràn đầy năng lượng nhỉ? Điều đó giúp tôi rất nhiều.</t>
+          <t>Hôm nay Doanh Doanh tràn đầy năng lượng thật đấy nhỉ? Nhờ thế mà ta đỡ vất vả hơn nhiều.</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tôi nghĩ mình nên nắm bắt cơ hội này. Đúng vậy. Tôi đến đây để tặng cậu Noctemints. Cậu có muốn ở bên tôi suốt đời không?</t>
+          <t>Tôi nghĩ mình nên nắm lấy cơ hội này. Đúng vậy, tôi đến đây để đưa cậu Noctemints. Cậu có muốn ở bên tôi suốt quãng đời còn lại không?</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Ông ấy từng là một chiến binh dũng cảm và khôn ngoan, ngay cả Echoes của ông cũng rất ấn tượng. So với ông, những người khác đều kém xa.</t>
+          <t>Ông ấy từng là một chiến binh dũng cảm và khôn ngoan, ngay cả những Tiếng Vọng của ông cũng rất ấn tượng. So với ông ấy, ai cũng chỉ là kẻ tầm thường.</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Vậy nên, cứ thoải mái hỏi tôi bất cứ điều gì liên quan đến Echo, nhưng hãy giữ mọi thứ khác ngoài lề nhé.</t>
+          <t>Vậy thì cứ hỏi tôi bất cứ điều gì liên quan đến Echo đi, nhưng những chuyện khác thì… đừng nhắc đến nhé.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Được rồi... Xin lỗi đã làm phiền cậu. Tớ xin phép đi đây.</t>
+          <t>Được rồi... Xin lỗi đã làm phiền cậu. Tôi xin phép đi đây.</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Hình như ông Jingzhu lại bị từ chối rồi.</t>
+          <t>Có vẻ như ông Jingzhu lại bị từ chối lần nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Ông nội Jingzhu, ông có sao không? Xin đừng buồn... C-C cháu sẽ làm mọi thứ để ông vui lên.</t>
+          <t>Ông Tinh Châu, ông không sao chứ? Đừng buồn nữa... C-cháu sẽ làm mọi cách để ông vui lên.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Hả? Sad à? Không hề! Dù có buồn đi chăng nữa, đó cũng chỉ là giả vờ thôi.</t>
+          <t>Hmm? Buồn à? Không hề! Dù có buồn đi chăng nữa, cũng chỉ là giả vờ thôi.</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Thất bại mười ba lần rồi, nhưng tôi không chịu bỏ cuộc! Dù là lần thứ mười bốn, mười lăm hay bao nhiêu nữa, tôi vẫn sẽ kiên trì...</t>
+          <t>Mười ba lần thất bại rồi, nhưng ta sẽ không bỏ cuộc đâu! Ta sẽ kiên trì, dù là lần thứ mười bốn, mười lăm hay xa hơn nữa...</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Sao tự dưng hăng thế?</t>
+          <t>Sao tự dưng cậu lại hăng máu thế?</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Vì ta đã quyết tâm trở thành người lính khôn ngoan và dũng cảm xứng với lý tưởng của Linghan!</t>
+          <t>Tao đã quyết tâm trở thành người lính khôn ngoan và dũng cảm xứng với lý tưởng của Linghan!</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Tôi thấy áy náy vì đã khiến nỗ lực của bạn trở nên vô ích.</t>
+          <t>Tao thấy áy náy vì đã làm công sức của mày đổ sông đổ bể.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Miễn là bạn không keo kiệt về khoản thù lao.</t>
+          <t>Miễn là cậu không keo kiệt về khoản trả công.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Thật thú vị khi được chứng kiến tất cả diễn ra.</t>
+          <t>Xem tất cả diễn ra như vậy thật là thú vị.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Cảm ơn nhé. Hai bạn thật tốt bụng!</t>
+          <t>Cảm ơn cậu. Hai cậu thật tốt bụng!</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Đừng lo. Tôi sẽ đảm bảo bạn nhận được đền bù thỏa đáng.</t>
+          <t>Đừng lo. Tôi sẽ đảm bảo cậu nhận được khoản đền bù xứng đáng.</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Ừm, hơi ngại nhỉ... Nhưng vui vẻ thì tốt cho sức khỏe mà, đúng không? Ít nhất mình cũng làm ai đó vui. Cũng không tệ lắm.</t>
+          <t>Thôi, hơi ngượng thật... Nhưng vui vẻ thì tốt cho sức khỏe mà, phải không? Ít ra ta cũng làm ai đó vui lên. Không tệ lắm.</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Ừm, hơi ngại nhỉ... Nhưng vui vẻ thì tốt cho sức khỏe mà, đúng không? Ít nhất mình cũng làm ai đó vui. Cũng không tệ lắm.</t>
+          <t>Thôi, hơi ngượng thật... Nhưng vui vẻ thì tốt cho sức khỏe mà, phải không? Ít ra ta cũng làm ai đó vui lên. Không tệ lắm.</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Mười ba lần từ chối liên tiếp... Có lẽ đã đến lúc tớ phải xem lại cách tiếp cận của mình...</t>
+          <t>Mười ba lần từ chối liên tiếp... Có lẽ đã đến lúc ta phải xem lại cách tiếp cận của mình...</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Có lẽ, Linghan chưa quen với những biểu lộ tình cảm trực tiếp và nồng nhiệt như vậy?</t>
+          <t>Hay là Linghan chưa quen với những biểu lộ tình cảm trực tiếp và nồng nhiệt như vậy?</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Cũng hợp lý... Bà Linghan trông khá nghiêm túc, có lẽ nên thay đổi chiến thuật nhỉ?</t>
+          <t>Hợp lý thật... Bà Linghan có vẻ khá nghiêm túc, có lẽ đã đến lúc đổi chiến thuật rồi nhỉ?</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hmm... Nên thử cách tiếp cận khác nào nhỉ?</t>
+          <t>Hừm... Nên thử cách tiếp cận khác nào nhỉ?</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Nói thêm về Echoes nhé?</t>
+          <t>Nói thêm về Echoes được không?</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Đúng vậy, có vẻ như chỉ có Echoes mới khiến cô ấy hứng thú.</t>
+          <t>Đúng vậy, có vẻ như chỉ có Echo mới khiến cô ấy hứng thú.</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tôi phải suy nghĩ kỹ về cách cải tiến Echo. Thực ra, hồi xưa đội trưởng đã dạy tôi rất nhiều, nhưng giờ tuổi già làm trí nhớ kém đi rồi.</t>
+          <t>Ta phải suy nghĩ kỹ về cách cải tiến Echo. Thực ra, hồi xưa đội trưởng đã dạy ta rất nhiều, nhưng giờ tuổi tác làm trí nhớ ta kém đi rồi.</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Được rồi, hôm nay đến đây thôi. Tôi cần về nhà suy nghĩ kỹ đã. Đây, đây là thù lao cho công sức của cậu hôm nay.</t>
+          <t>Được rồi, hôm nay tạm dừng ở đây thôi. Tôi cần về nhà suy nghĩ kỹ đã. Đây, tiền công cho hôm nay của cậu.</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>{PlayerName}, are you ready?</t>
+          <t>{PlayerName}, cậu đã sẵn sàng chưa?</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Chưa xong.</t>
+          <t>Chưa.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Tôi sẵn sàng rồi.</t>
+          <t>Tao sẵn sàng rồi.</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Đừng lo. Hãy từ từ mài giũa vũ khí của bạn.</t>
+          <t>Đừng lo. Cậu cứ từ từ mài vũ khí đi.</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Tuyệt quá, bắt đầu thôi! Ông Jingzhu bảo đây là thời điểm tốt nhất để bắt Echo, và tớ đã sẵn sàng săn một đống luôn!</t>
+          <t>Tuyệt quá, bắt đầu thôi! Ông Jingzhu bảo giờ là lúc tốt nhất để bắt Echo, và tớ đã sẵn sàng săn một đống luôn!</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Ông Jingzhu, ông đã điều trị xong rồi ạ? Nhanh thế!</t>
+          <t>Ông nội Jingzhu, ông điều trị xong rồi à? Nhanh thế!</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Đừng để tuổi già của ông già này đánh lừa cô. Ta vẫn còn khỏe và mấy vết thương này chẳng làm ta chậm lại chút nào!</t>
+          <t>Đừng để vẻ ngoài của lão già này đánh lừa con. Lão vẫn còn khỏe lắm, mấy vết thương này chẳng làm lão chậm lại được đâu!</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Thật sao? Ừm... dù sao cậu có vẻ đã ổn rồi.</t>
+          <t>Thật á? Ừm... dù nhìn cậu có vẻ ổn rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Tất nhiên! Tôi đã quen với vết thương rồi. Dù sao giờ tôi cũng thấy ổn rồi. Chúng ta đi không?</t>
+          <t>Tất nhiên rồi! Tôi quen với vết thương mà. Dù sao giờ tôi cũng thấy khỏe hẳn rồi. Chúng ta đi thôi chứ?</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Ông có đi cùng chúng cháu không, ông Jingzhu?</t>
+          <t>Ông có đi cùng chúng cháu không, ông nội Jingzhu?</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Haha, đừng lo! Lão già này ngày xưa cũng từng là tay cừ khôi đấy! Dù giờ đã già, lão vẫn có thể đương đầu với mọi hiểm nguy.</t>
+          <t>Haha, đừng lo! Ông già này ngày xưa cũng từng là tay cừ khôi đấy! Dù giờ đã già, nhưng đối phó nguy hiểm thì vẫn còn trâu à.</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Được rồi, ông Jingzhu, hứa với cháu là ông sẽ giữ gìn sức khỏe nhé. Nếu có gì nguy hiểm xảy ra, đừng cố chịu đựng một mình. Hãy gọi cháu ngay lập tức!</t>
+          <t>Được rồi, ông Jingzhu à, ông nhớ phải giữ gìn sức khỏe nhé. Nếu có gì nguy hiểm, đừng có cố chịu đựng mà hãy gọi cháu ngay lập tức!</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Dù sao thì đây cũng là nhiệm vụ của Đội Tuần Tra mà.</t>
+          <t>Dù sao, đây cũng là một phần nhiệm vụ của Đội Tuần Tra mà.</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Sắp tới nơi rồi. Hãy đi sát tôi nhé!</t>
+          <t>Sắp tới nơi rồi. Đừng rời xa tao nhé!</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Ông Jingzhu, ông có khỏe không?</t>
+          <t>Ông Tinh Châu, ông có sao không ạ?</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Đúng vậy. Có cả đống Tacet Discord quanh đây. Bạn nghĩ chúng ta nên bắt con nào trước?</t>
+          <t>Đúng đấy. Xung quanh có cả đống Tacet Discord. Cậu nghĩ chúng ta nên bắt con nào trước?</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Người ấn tượng.</t>
+          <t>Kẻ ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Người đáng gờm.</t>
+          <t>Kẻ mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chính xác, đó là mục tiêu của tôi. Hãy cùng nhắm đến việc bắt được con ấn tượng nhất!</t>
+          <t>Chính xác, đó là mục tiêu của ta. Hãy nhắm đến con mồi ấn tượng nhất thôi!</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Những kẻ mạnh mẽ luôn là ấn tượng nhất. Đó là một và như nhau.</t>
+          <t>Những kẻ mạnh mẽ bao giờ cũng gây ấn tượng nhất. Đó là lẽ đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>À, để tôi nghĩ xem... con mạnh mẽ và ấn tượng nhất quanh đây là... Havoc Warrior! Hãy chụp lại nó!</t>
+          <t>À, để tôi nghĩ xem... kẻ mạnh nhất và đáng gờm nhất ở đây là... Havoc Warrior! Bắt lấy nó thôi!</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Tất nhiên! Hồi còn sung sức, cùng thuyền trưởng của tôi, chúng tôi đã bắt được đủ loại Tacet Discords...</t>
+          <t>Tất nhiên rồi! Hồi còn sung sức, cùng đội trưởng, chúng tôi đã bắt sống đủ loại Tacet Discord...</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Hửm? Có mấy Havoc Warrior phía trước. Let’s go!</t>
+          <t>Hửm? Có mấy tên Chiến Binh Havoc phía trước. Đi nào!</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hihi, biết ngay là chúng ta làm được mà! Giờ chúng ta có Echo rồi, dễ ợt.</t>
+          <t>Hehe, biết ngay là chúng ta làm được mà! Giờ có Echo rồi, dễ như ăn kẹo ấy.</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Này {PlayerName}, nhanh hấp thụ nó đi trước khi nó biến mất!</t>
+          <t>Này {PlayerName}, nhanh hấp thụ nó đi trước khi nó biến mất đấy!</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Ông nội Jingzhu xem này! Những lưỡi hái khổng lồ này ngầu quá phải không?</t>
+          <t>Ông nội Jingzhu xem này! Những lưỡi hái khổng lồ này ngầu quá phải không ạ?</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Ừm, cũng không tệ. Lần này cô ấy chắc sẽ hài lòng.</t>
+          <t>Ừm, không tệ. Lần này cô ấy chắc sẽ hài lòng.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Ước gì lần này, cô ấy sẽ ở lại đủ lâu để nghe tôi nói trước khi bỏ đi...</t>
+          <t>Ước gì lần này thôi, cô ấy chịu ở lại nghe tôi nói hết trước khi bỏ đi...</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ồ, mình có ý này! Nếu chúng ta biến thành Lưỡi Hái thì chắc chắn sẽ gây ấn tượng với cô ấy!</t>
+          <t>Oa, em có ý này! Nếu chúng ta biến thành Scythe thì chắc chắn sẽ gây ấn tượng với cô ấy!</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Ôi, làm ơn đừng thế, cháu yêu. Cô ấy có thể sợ đấy. Hay là chúng ta hãy tập hợp thêm vài người nữa, cho chắc ăn.</t>
+          <t>Ôi, đừng làm thế, cháu yêu. Cô ấy có thể sợ đấy. Hay chúng ta tìm thêm vài người nữa cho chắc, được không?</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Havoc Warrior quả thực ấn tượng, nhưng chỉ dựa vào một Echo có lẽ chưa đủ để chiếm được trái tim cô ấy...</t>
+          <t>Chiến Binh Hỗn Loạn quả là ấn tượng thật, nhưng chỉ dựa vào một Echo thôi thì có lẽ chưa đủ để chiếm được trái tim cô ấy đâu...</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Chúng ta cần một bộ sưu tập, một màn trưng bày nhiều Echoes để thực sự gây ấn tượng!</t>
+          <t>Chúng ta cần một bộ sưu tập, một buổi trưng bày nhiều Echo để thực sự gây ấn tượng!</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Ừ! Có cả đàn Echoes đi theo thì đúng là gây chú ý thật, nhưng làm sao để có thêm nhỉ?</t>
+          <t>Ừa! Có cả đàn Echo đi theo sau thì đúng là oách thật, nhưng làm sao để bắt thêm được nhỉ?</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Đến &lt;ano=A place where TDs gather&gt;Bãi Tacet&lt;/ano&gt; nào! Tacet Discord bị thu hút đến nơi này như thiêu thân thấy lửa vậy.</t>
+          <t>Đến &lt;ano=A place where TDs gather&gt;Tổ Tacet&lt;/ano&gt;! Tacet Discord bị hút về nơi đó như bướm đêm lao vào lửa.</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Shh... Tôi cảm nhận được rồi. Những tần số của Trường Tacet...</t>
+          <t>Suỵt... Ta cảm nhận được rồi. Những tần số của Tổ Tacet...</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Có một Tacet Field gần đây!</t>
+          <t>Có một Tổ Tacet gần đây!</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Wow, quả thật có Tacet Field! Ông Jingzhu, ông biết nhiều thật đấy!</t>
+          <t>Ồ, quả thật có Tổ Tacet! Ông Jingzhu, ông biết nhiều thật đấy!</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Haha, tôi đã bảo cậu rồi mà, lúc còn trẻ ông già này cũng từng trải qua không ít cuộc phiêu lưu!</t>
+          <t>Hehe, ta đã bảo rồi mà, hồi trẻ ta cũng từng trải qua không ít cuộc phiêu lưu đấy chứ!</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Giờ là lúc cậu tỏa sáng rồi. Dọn sạch Trường Tacet này và cậu sẽ bắt được vài Echoes đấy.</t>
+          <t>Giờ là lúc cậu tỏa sáng. Dọn sạch Tổ Tacet này đi, và cậu sẽ bắt được vài Echo đấy.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Phù, cuối cùng cũng xong! Để xem nào...</t>
+          <t>Phù, xong rồi! Để tao xem nào...</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Chà, chỉ còn hai Echoes nữa thôi! {PlayerName}, cậu thật may mắn!</t>
+          <t>Ôi, chỉ còn hai Echo nữa thôi! {PlayerName}, cậu đúng là may mắn quá đi!</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Biết đấy, tỷ lệ Echoes xuất hiện sau khi hạ gục Tacet Discord đã thấp, huống chi là có được hai cái cùng lúc!</t>
+          <t>Cậu biết không, tỷ lệ xuất hiện Echo sau khi đánh bại Tacet Discord đã thấp rồi, huống chi là có được hai cái cùng lúc!</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Nghe nói Terminal càng mạnh thì càng dễ xuất hiện Echoes. Đó là vì... vì... À thôi, Terminal của cậu hẳn là cực kỳ mạnh rồi! Right không?</t>
+          <t>Nghe nói Thiết bị đầu cuối càng mạnh thì càng dễ xuất hiện Echo. Tại vì... à thôi, dù sao Thiết bị của cậu cũng phải siêu mạnh rồi! Đúng không?</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Chào cậu, tớ là Jingzhu đây! Tớ lại liên lạc để nhờ sự giúp đỡ của các cậu trẻ tuổi rồi.</t>
+          <t>Này, ông đây, Jingzhu! Lại phải nhờ đến sự giúp đỡ của các cháu trẻ một lần nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Anh khỏe không?</t>
+          <t>Cậu sao rồi?</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tôi có thể giúp gì cho bạn?</t>
+          <t>Tôi có thể làm gì cho cậu?</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Như thường lệ, tôi vẫn ổn mà!</t>
+          <t>Như thường lệ, ta vẫn ổn mà!</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Một Kẻ Lang Thang Bóng Đêm dũng cảm như ta sẽ không nao núng trước vài trở ngại!</t>
+          <t>Một Kẻ Tuần Đêm dũng mãnh như ta sẽ không bị khuất phục bởi vài thất bại nhỏ!</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Kể từ lần gặp cuối, tôi đã suy nghĩ về một phương pháp thực tế hơn...</t>
+          <t>Từ lần gặp trước đến giờ, tớ vẫn suy nghĩ về một phương pháp thực tế hơn...</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Và cuối cùng thì mình cũng đã sáng chế ra một cái! Háo hức muốn đưa vào sử dụng quá đi!</t>
+          <t>Và cuối cùng ta cũng nghĩ ra được một kế! Háo hức muốn thực hiện ngay thôi!</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Anh cần giúp không?</t>
+          <t>Cậu cần giúp gì không?</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Hehe, đúng rồi. Tôi đã suy nghĩ kỹ và thực sự cần sự giúp đỡ của các cậu.</t>
+          <t>Hehe, đúng vậy. Tớ đã suy nghĩ kỹ và thấy mình cần sự trợ giúp của các cậu trẻ tuổi.</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Nghe cậu không được hào hứng lắm, nhưng không sao. Khi đến nơi, cậu sẽ ngay lập tức bị thuyết phục rằng kế hoạch của tôi sẽ thành công lần này!</t>
+          <t>Nghe cậu không hào hứng lắm, nhưng không sao. Khi đến nơi, cậu sẽ bị thuyết phục ngay rằng kế hoạch của tôi sẽ thành công lần này!</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Ta sẽ đợi cậu ở Nhà hát Jinzhou, và tên Tuần tra viên tóc đỏ kia cũng sẽ tham gia cùng chúng ta.</t>
+          <t>Ta sẽ đợi cậu ở Nhà hát Jinzhou, và tên Tuần Tra tóc đỏ kia cũng sẽ tham gia cùng chúng ta.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Và đừng lo, ta đã chuẩn bị sẵn thù lao cho ngươi. Ta sẽ không để ngươi làm không công đâu.</t>
+          <t>Đừng lo, tao đã chuẩn bị sẵn tiền trả công cho cậu rồi. Tao không để cậu làm không công đâu.</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Được rồi, thôi được...</t>
+          <t>Được rồi, đồng ý...</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Được rồi, hẹn gặp lại sau!</t>
+          <t>Được rồi, hẹn gặp lại sau nhé!</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Được rồi, hẹn gặp lại sau!</t>
+          <t>Được rồi, hẹn gặp lại sau nhé!</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Này! Mọi người đều ở đây rồi!</t>
+          <t>Này! Mọi người đều đến rồi!</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Khi nghe tin ông Jingzhu cần giúp đỡ, tôi lập tức lao đến đây bằng tuyệt kỹ overdash siêu đỉnh của mình!</t>
+          <t>Khi nghe ông Jingzhu cần người giúp, tao phóng ngay tới đây bằng tuyệt chiêu overdash bá đạo của mình!</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Không cần vội. Nghỉ ngơi chút đi, trẻ con.</t>
+          <t>Không cần vội vàng đâu. Nghỉ ngơi một chút đi, cậu bé.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đừng lo, tôi tràn đầy năng lượng mà! Vậy ông Jingzhu, kế hoạch là gì ạ?</t>
+          <t>Đừng lo, tớ tràn đầy năng lượng! Vậy, ông Jingzhu, kế hoạch là gì ạ?</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Được rồi. Phải nói là gợi ý của {PlayerName} khá thực tế. Hãy tìm một chủ đề khiến cô ấy hứng thú rồi từ từ tiến hành...</t>
+          <t>Được rồi. Phải nói là ý kiến của {PlayerName} khá thực tế. Hãy tìm thứ gì đó khiến cô ấy hứng thú rồi từ từ tiến hành…</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Vậy nên, tôi đã nghĩ ra kế hoạch nâng cấp Echo. Khi chúng ta làm cho Lưỡi Hái mạnh hơn, tôi sẽ sẵn sàng trình bày nó với cô ấy.</t>
+          <t>Vậy nên, mình đã lên kế hoạch cải tiến Echo. Khi nào làm Scythe mạnh hơn, mình sẽ trình bày ý tưởng này với cô ấy.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Ừ, còn gì nữa không? The Scythes đã khá ấn tượng rồi. Chúng ta có thể nâng cấp thêm không?</t>
+          <t>Ừ, còn cách nào khác không? Lưỡi Hái đã khá ấn tượng rồi. Giờ tăng thêm tí nữa được không?</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Để tôi chia sẻ một bí mật nhỏ với bạn. Ở Tacet Fields còn có một tài sản quý giá khác... gọi là Tuner!</t>
+          <t>Để ta kể cho cậu một bí mật nho nhỏ. Trong Tổ Tacet còn có một tài sản quý giá khác... gọi là Bộ Điều Tần!</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Tuners?</t>
+          <t>Điều Chỉnh Giả à?</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đúng vậy, Tuner có khả năng tinh chỉnh tần số của Echoes, loại bỏ tạp âm không mong muốn và tăng cường sức mạnh của chúng!</t>
+          <t>Đúng rồi, Tuner có khả năng tinh chỉnh tần số của Echo, loại bỏ tạp âm và tăng cường sức mạnh cho chúng!</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>À, đúng rồi! Đó là thứ tròn hay vuông ấy nhỉ? Sao mình lại quên được nhỉ?</t>
+          <t>À đúng rồi! Cái đó tròn hay vuông ấy nhỉ? Sao mình lại quên được chứ?</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Mục tiêu hôm nay của chúng ta là thu thập vài Tuner từ Tacet Fields.</t>
+          <t>Mục tiêu hôm nay của chúng ta là thu thập vài Tuner từ các Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Tuyệt! Để có những Echoes mạnh mẽ hơn! Bắt đầu thôi!</t>
+          <t>Tuyệt! Để có Echo mạnh hơn! Ta tiến thôi!</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>À, cuối cùng cũng đến rồi. Nó ở ngay gần đây thôi.</t>
+          <t>À, cuối cùng cũng đến rồi. Chỗ đó ngay gần đây thôi.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Xin lỗi, tôi cần nghỉ ngơi một chút. Mọi việc còn trông cậy vào các cậu rồi!</t>
+          <t>Xin lỗi, nhưng ta cần nghỉ ngơi một chút. Mọi việc còn trông cậy vào các cháu đấy!</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Xuất sắc! {PlayerName}, cậu thật sự làm chủ được rồi!</t>
+          <t>Chuẩn luôn! {PlayerName}, cậu tiến bộ thật đấy!</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Chúng ta đã tìm thấy vài Tuner! Phải thừa nhận là tôi cũng thắc mắc sao cậu lại thoải mái như vậy khi ở nơi hoang dã.</t>
+          <t>Chúng ta tìm thấy vài cái Tuner rồi! Phải thừa nhận là mình cũng thắc mắc sao cậu lại thoải mái thế khi ở ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Nhưng giờ biết cậu từng là Midnight Ranger thì mọi thứ hợp lý quá!</t>
+          <t>Nhưng giờ khi biết anh từng là một Midnight Ranger, mọi chuyện đều hợp lý cả!</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Đội trưởng của tôi đã dạy tôi rất nhiều... từ cách phát hiện Tacet Field đến nhận diện các loại Tacet Discord, thậm chí cả những nơi tìm thấy Tuner...</t>
+          <t>Đội trưởng của tôi đã dạy tôi rất nhiều… từ cách phát hiện Tổ Tacet đến nhận diện các Tacet Discord khác nhau, thậm chí cả những nơi tìm thấy Tuner…</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Tuy nhiên, ký ức thường đánh lừa khi ta già đi, nên tôi phải tận mắt chứng kiến mới dám chắc.</t>
+          <t>Nhưng ký ức thường đánh lừa ta khi về già, nên tao phải tận mắt nhìn thấy mới dám chắc.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Ngay cả khi ở nơi hoang dã, ta vẫn phải nhờ các cậu trẻ giúp ta đạt được mục tiêu.</t>
+          <t>Ngay cả nơi hoang dã, ta vẫn phải nhờ các cậu trẻ giúp ta hoàn thành mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nhưng thôi đủ buồn rồi. Miễn là Echo trở nên mạnh mẽ hơn, tôi hài lòng.</t>
+          <t>Nhưng thôi đừng buồn nữa. Miễn là Echo ngày càng mạnh mẽ, ta hài lòng rồi.</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Hừm, không tệ đâu. Ngươi đã khơi gợi lại những ký ức về thời huy hoàng của ta.</t>
+          <t>Hmm, không tồi. Cậu đã khơi gợi lại những ký ức huy hoàng ngày xưa của ta.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Linghan chắc sẽ rất vui khi thấy thứ này, cậu thấy thế nào?</t>
+          <t>Lăng Hàn chắc sẽ rất vui khi thấy điều này, cậu không nghĩ vậy sao?</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Hãy nhanh chóng quay về cho cô ấy xem!</t>
+          <t>Ta mau về cho cô ấy xem thôi!</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Kỳ lạ thật. Thật bất thường khi Linghan không ra ngoài tắm nắng vào giờ này. Cô ấy có thể đang ở trong nhà không nhỉ?</t>
+          <t>Kỳ lạ thật. Thường giờ này Linghan đã ra ngoài tắm nắng rồi chứ. Lẽ nào cô ấy ở trong nhà à?</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Không trả lời...</t>
+          <t>Không trả lời gì cả...</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Something's not right. Linghan thường tránh đi quá xa vì trí nhớ của cô ấy không còn tốt như trước...</t>
+          <t>Có gì đó không ổn. Linghan thường không đi xa thế này vì trí nhớ của cô ấy không còn tốt như xưa...</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ừ, tôi cũng thấy có gì đó kỳ lạ. Hỏi thăm quanh khu phố xem sao.</t>
+          <t>Ừ, tớ cũng thấy có gì đó kỳ kỳ. Đi hỏi thăm quanh khu này xem sao.</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Giao phó cho tôi đi! Tôi biết khu vực này như lòng bàn tay. Tôi sẽ hỏi mọi người xem có ai thấy Bà Linghan không.</t>
+          <t>Tin ở tao đi! Tao biết khu này rõ như lòng bàn tay. Tao sẽ đi hỏi tất cả những người có thể xem họ có thấy bà Linghan không.</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Có vẻ cô ấy đã ra ngoài từ sáng sớm.</t>
+          <t>Có vẻ sáng nay cô ấy đã ra ngoài từ sớm.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Lạ nhỉ? Nghe nói dạo này cô ấy không được khỏe, hiếm khi ra ngoài. Thay vào đó, cô ấy dành hàng giờ phơi nắng ngay trước cửa nhà.</t>
+          <t>Kỳ lạ thật đấy. Nghe nói dạo này cô ấy không được khỏe, hầu như không ra ngoài. Thay vào đó, cô ấy dành hàng giờ ngồi phơi nắng ngay trước cửa nhà.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Nhưng hôm nay cô ấy đi thẳng ra ngoài, và tôi không biết cô ấy đi đâu.</t>
+          <t>Nhưng hôm nay cô ấy đi thẳng ra ngoài, và ta chẳng biết cô ấy đi đâu.</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Hiểu rồi, cảm ơn đã cho tôi biết. Tôi sẽ hỏi người khác xem có thể tìm thêm thông tin không.</t>
+          <t>Hiểu rồi, cảm ơn đã báo cho tôi. Tôi sẽ hỏi thêm người khác xem có tìm được thêm thông tin không.</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Hello, cho tôi hỏi tên bạn là gì?</t>
+          <t>Xin chào, cho tôi hỏi tên của bạn được không?</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hello, mình là Lanqing. Mình mới chuyển đến. Bạn là Patroller à? Có chuyện gì xảy ra quanh đây không?</t>
+          <t>Chào cậu, mình là Lanqing. Mình mới chuyển đến. Cậu là Tuần Tra Viên à? Có chuyện gì xảy ra ở quanh đây không?</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Này, phiền cậu cho tôi hỏi chút được không? Hôm nay cậu có thấy bà Linghan ở đâu không?</t>
+          <t>Này, hỏi tí được không? Hôm nay cậu có thấy bà Linghan đâu không?</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Ý cậu là quý cô thích Echoes đúng không? Hôm nay tôi không thấy cô ấy ở quanh đây, tiếc thật.</t>
+          <t>Cậu đang nói về quý cô thích Echoes phải không? Hôm nay tôi không thấy cô ấy đâu cả, tiếc thật.</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Tôi đã gặp cô ấy vài lần. Cô ấy có vẻ tốt.</t>
+          <t>Tớ đã gặp cô ấy vài lần. Cô ấy có vẻ tốt bụng.</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Nhưng trông cô ấy lúc nào cũng hơi mệt mỏi, và trí nhớ có vẻ không được tốt lắm.</t>
+          <t>Nhưng trông cô ấy lúc nào cũng có vẻ không được khỏe, và trí nhớ cũng có phần lơ mơ.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tôi nghe nói cô ấy đang gặp vấn đề sức khỏe nghiêm trọng. Chắc hẳn cô ấy rất khó khăn.</t>
+          <t>Nghe nói cô ấy đang gặp vấn đề sức khỏe nghiêm trọng. Chắc là rất khó khăn cho cô ấy.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>*Nức nở* Ông ơi! Cuối cùng cũng có người giúp! Bọn cháu sợ quá...</t>
+          <t>*Khóc nức nở* Ông ơi! Cuối cùng cũng có người đến giúp! Cháu sợ quá...</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Không, không, đừng khóc. Kể cho ông nghe chuyện gì đã xảy ra.</t>
+          <t>Không, không, không, đừng khóc cháu ơi. Kể cho ông nghe chuyện gì đã xảy ra nào.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Bà nội đi từ sáng sớm, khi bố phát hiện và đi tìm thì bà đã biến mất rồi! *Khóc nức nở*</t>
+          <t>Sáng nay bà đi sớm lắm, bố phát hiện ra liền đi tìm thì... bà biến mất rồi! *Nức nở*</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Nếu bà lại đi lạc thì sao...?</t>
+          <t>Nếu bà lại đi lạc nữa thì sao...?</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Đừng lo, Yingying. Bà sẽ ổn thôi. Bà sẽ sớm về nhà mà.</t>
+          <t>Đừng lo, Yingying. Bà sẽ ổn thôi. Bà sẽ về nhà sớm thôi.</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tôi phải suy nghĩ kỹ lý do Linghan ra ngoài hôm nay. Chắc hẳn có mục đích nào đó.</t>
+          <t>Ta phải suy nghĩ kỹ xem hôm nay Linghan ra ngoài vì lý do gì. Chắc chắn phải có mục đích đằng sau.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>À, tôi hiểu rồi... Hôm nay là... Tôi biết cô ấy đang ở đâu. Đừng lo. Tôi sẽ đưa cô ấy về nhà an toàn.</t>
+          <t>À, ra vậy... Hôm nay là... Tôi biết con bé đang ở đâu. Đừng lo. Tôi sẽ đưa nó về nhà an toàn.</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Cần giúp đỡ không?</t>
+          <t>Cần giúp đỡ gì không?</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Để chúng tôi giúp.</t>
+          <t>Hãy để chúng tôi giúp cậu.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Thật yên tâm khi có sự hỗ trợ của cậu. Về vấn đề an toàn của Linghan, càng nhiều người giúp đỡ càng tốt.</t>
+          <t>Có cậu hỗ trợ thật yên tâm. Về vấn đề an toàn của Linghan, càng nhiều người giúp đỡ càng tốt.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Cảm ơn các cháu... Lời nói không đủ diễn tả lòng biết ơn của ta.</t>
+          <t>Cảm ơn các cháu... Lời nói không thể diễn tả hết lòng biết ơn của ta.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Đúng vậy! Càng nhiều người quan sát, chúng ta càng nhanh tìm ra bà Linghan.</t>
+          <t>Ừ! Càng nhiều người quan sát, chúng ta càng nhanh tìm thấy bà Linghan thôi!</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tôi nghĩ cô ấy có thể đã đến cái hang gần rìa Jinzhou.</t>
+          <t>Tao đoán cô ấy có thể đã đến cái hang gần rìa Jinzhou ấy.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Một cái hang à? Bọn Tacet Discord rất thích tụ tập ở những nơi như thế. Mau đến xem thôi!</t>
+          <t>Hang động à? Tacet Discord rất thích tụ tập ở những nơi như thế. Mau đến xem thôi!</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Nơi này rộng quá! Làm sao chúng ta tìm được cô ấy đây? Thật bực mình!</t>
+          <t>Chỗ này rộng quá! Làm sao chúng ta tìm được cô ấy bây giờ? Tức thật đấy!</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Chúng ta nên chia nhau ra không?</t>
+          <t>Chúng ta có nên chia nhau ra không?</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Ta có manh mối nào khác không?</t>
+          <t>Chúng ta còn manh mối nào khác không?</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Bình tĩnh nào, nhóc. Có một manh mối có thể giúp chúng ta tìm thấy Linh Hàn nhanh chóng.</t>
+          <t>Bình tĩnh nào, cậu bé. Có một manh mối có thể giúp ta tìm Linghan nhanh hơn đấy.</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Giờ cậu nhắc tới, ta chợt nhớ ra điều gì đó. Có thể nó sẽ giúp chúng ta tìm thấy Linghan nhanh chóng.</t>
+          <t>Nhắc mới nhớ, có điều gì đó vừa lóe lên trong đầu ta. Có thể giúp chúng ta tìm Linghan nhanh hơn đấy.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Thời chúng ta, phải dựa vào kinh nghiệm để xác định vị trí Tacet Discord, nhưng nghe nói giờ đã có công nghệ tiên tiến hơn rồi.</t>
+          <t>Thời chúng tôi, chúng tôi dựa vào kinh nghiệm để xác định vị trí Tacet Discord, nhưng tôi nghe nói giờ đã có những công nghệ tiên tiến hơn rồi.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Đúng rồi! Quả bầu đã được nâng cấp chức năng tìm kiếm. Thử dùng nó để phát hiện Tacet Discord gần đây xem sao.</t>
+          <t>Ừ! Quả bầu vừa được nâng cấp chức năng tìm kiếm đấy. Thử xem có phát hiện được Tacet Discord nào gần đây không.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Để tôi thử...</t>
+          <t>Để ta thử xem...</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Dùng nó như thế nào?</t>
+          <t>Dùng cái này như thế nào?</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Được rồi! Tôi sẽ hướng dẫn bạn qua tất cả.</t>
+          <t>Đúng rồi! Tớ sẽ dẫn đường cho cậu qua chỗ này.</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Ồ, công nghệ mới này thật tuyệt vời! Chúng ta đã tìm thấy cô ấy trong nháy mắt.</t>
+          <t>Ôi, công nghệ mới này tuyệt quá! Tìm thấy cô ấy nhanh như chớp luôn.</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Đừng chần chừ nữa. Cố lên, Linghan! Chúng ta đang đến!</t>
+          <t>Đừng có chậm chạp nữa. Chờ tí, Linghan! Bọn mình đang tới rồi!</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Nơi này thực sự nguy hiểm. Bà Linghan sức khỏe không tốt. Sao bà ấy lại đến đây...</t>
+          <t>Nơi này nguy hiểm thật sự. Bà Linghan sức khỏe không tốt. Sao bà lại đến đây...</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Cô ấy chắc hẳn đến đây để thu thập Echo của Nghệ sĩ Sáo. Dù sao thì hôm nay là... một ngày đặc biệt.</t>
+          <t>Chắc hẳn cô ấy đến đây để thu thập Echo của Flautist. Suy cho cùng, hôm nay là... một ngày đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Hôm nay ngày gì đặc biệt à?</t>
+          <t>Ngày đặc biệt gì?</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Chính Linghan đã đề xuất một chiến thuật xuất sắc. Với hiểu biết sâu sắc về Echoes, cô đề nghị sử dụng chúng để đẩy lùi cuộc tấn công của kẻ địch.</t>
+          <t>Chính Linghan đã đề xuất một chiến lược xuất sắc. Với hiểu biết sâu sắc về Echo, cô ấy đề nghị tận dụng chúng để đẩy lùi cuộc tấn công của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Để giảm thiểu thương vong, cô đã dẫn cả đội đến đây thu thập hàng trăm Echoes của Flautist.</t>
+          <t>Để giảm thiểu thương vong, cô ấy đã dẫn cả đội đến đây thu thập hàng trăm Tiếng Vọng Kèn Flautist.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Cô ấy cũng từng là một Midnight Ranger sao?</t>
+          <t>Cô ấy cũng là một Midnight Ranger sao?</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Yes...</t>
+          <t>Ừ...</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Này, người có mái tóc bạc đằng kia chẳng phải... Bà Linghan sao! BÀ LINGHAN! Ở ĐÂY NÈ!</t>
+          <t>Này, người tóc bạc kia không phải... Bà Linghan sao! BÀ LINGHAN! Ở ĐÂY NÈ!</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Chết rồi! Cô ấy ở quá xa để nghe chúng ta!</t>
+          <t>Chết tiệt! Cô ấy ở quá xa, không nghe thấy đâu!</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Không! Lũ Tacet Discord đang tiến gần đến cô ấy!</t>
+          <t>Không! Bọn Tacet Discord đang tiến đến gần cô ấy!</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Chết tiệt! Từ khoảng cách này, chúng ta thậm chí không thể dùng lao vượt để đuổi kịp!</t>
+          <t>Ôi trời! Khoảng cách này thì bay vượt cũng không kịp đâu!</t>
         </is>
       </c>
     </row>
